--- a/reports/module-data-integration-audit/2026-07-27/CURRENT_MODULE_DATA_INVENTORY.xlsx
+++ b/reports/module-data-integration-audit/2026-07-27/CURRENT_MODULE_DATA_INVENTORY.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="1" r:id="R72a70fd0161240ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="1" r:id="R6f846340a2db41f4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -7813,7 +7813,7 @@
         <x:v>Static repo audit only: requires live row profiling for nulls, duplicates, stale rows, broken links</x:v>
       </x:c>
       <x:c r="N104" s="5" t="str">
-        <x:v>scripts/qa/home-know-data-gate.mjs; src/lib/tower/tower-budget-rollups.ts; src/lib/tower/tower-semantic-projection.ts</x:v>
+        <x:v>scripts/audit/build-module-migration-sunset-backlog.mjs; scripts/qa/home-know-data-gate.mjs; src/lib/tower/tower-budget-rollups.ts; src/lib/tower/tower-semantic-projection.ts</x:v>
       </x:c>
       <x:c r="O104" s="5" t="str"/>
       <x:c r="P104" s="5" t="str">
@@ -7838,7 +7838,7 @@
         <x:v>id; client_id; tenant_key; canonical_record_id; record_type; record_subtype; title; source_id; source_file_id; source_system; source_record_id; source_file; source_sheet; source_row_number; owner; steward_owner; last_synced_at; last_validated_at; confidence; freshness_status; evidence_pointer; lifecycle_state; superseded_by_record_id; payload_hash</x:v>
       </x:c>
       <x:c r="W104" s="5" t="str">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="X104" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>

--- a/reports/module-data-integration-audit/2026-07-27/CURRENT_MODULE_DATA_INVENTORY.xlsx
+++ b/reports/module-data-integration-audit/2026-07-27/CURRENT_MODULE_DATA_INVENTORY.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="1" r:id="R6f846340a2db41f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="1" r:id="Rcd81e3b5fc074fa6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -323,15 +323,16 @@
     <x:col min="13" max="13" width="16" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="21" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="20" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="24" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="25" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="28" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="24" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="23" hidden="0" customWidth="1"/>
-    <x:col min="21" max="21" width="16" hidden="0" customWidth="1"/>
-    <x:col min="22" max="22" width="25" hidden="0" customWidth="1"/>
-    <x:col min="23" max="23" width="24" hidden="0" customWidth="1"/>
-    <x:col min="24" max="24" width="14" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="39" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="22" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="25" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="28" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="24" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="23" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="16" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="25" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="24" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
@@ -381,30 +382,33 @@
         <x:v>metrics_produced</x:v>
       </x:c>
       <x:c r="P1" s="9" t="str">
-        <x:v>canonical_equivalent</x:v>
+        <x:v>provisional_canonical_object_family</x:v>
       </x:c>
       <x:c r="Q1" s="9" t="str">
+        <x:v>mapping_confidence</x:v>
+      </x:c>
+      <x:c r="R1" s="9" t="str">
         <x:v>future_classification</x:v>
       </x:c>
-      <x:c r="R1" s="9" t="str">
+      <x:c r="S1" s="9" t="str">
         <x:v>classification_rationale</x:v>
       </x:c>
-      <x:c r="S1" s="9" t="str">
+      <x:c r="T1" s="9" t="str">
         <x:v>migration_complexity</x:v>
       </x:c>
-      <x:c r="T1" s="9" t="str">
+      <x:c r="U1" s="9" t="str">
         <x:v>cutover_requirement</x:v>
       </x:c>
-      <x:c r="U1" s="9" t="str">
+      <x:c r="V1" s="9" t="str">
         <x:v>source_files</x:v>
       </x:c>
-      <x:c r="V1" s="9" t="str">
+      <x:c r="W1" s="9" t="str">
         <x:v>parsed_columns_sample</x:v>
       </x:c>
-      <x:c r="W1" s="9" t="str">
+      <x:c r="X1" s="9" t="str">
         <x:v>code_reference_count</x:v>
       </x:c>
-      <x:c r="X1" s="9" t="str">
+      <x:c r="Y1" s="9" t="str">
         <x:v>confidence</x:v>
       </x:c>
     </x:row>
@@ -456,27 +460,30 @@
         <x:v>knowledge.program</x:v>
       </x:c>
       <x:c r="Q2" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R2" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R2" s="5" t="str">
+      <x:c r="S2" s="5" t="str">
         <x:v>Review workflow state remains in Moves; accepted decisions may emit canonical decision/evidence records later.</x:v>
       </x:c>
-      <x:c r="S2" s="5" t="str">
+      <x:c r="T2" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T2" s="5" t="str">
+      <x:c r="U2" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U2" s="5" t="str">
+      <x:c r="V2" s="5" t="str">
         <x:v>supabase/migrations/20260628160000_move_artifact_review_decisions.sql</x:v>
       </x:c>
-      <x:c r="V2" s="5" t="str">
+      <x:c r="W2" s="5" t="str">
         <x:v>id; tenant_id; tenant_key; move_id; phase; artifact_id; artifact_version; reviewer_user_id; reviewer_email; decision; rationale; carried_forward_caveats; missing_evidence; allowed_next_action; ready_for_p3_draft; ready_for_p3_final; p2_final_approved; created_at</x:v>
       </x:c>
-      <x:c r="W2" s="5" t="str">
+      <x:c r="X2" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X2" s="5" t="str">
+      <x:c r="Y2" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -528,27 +535,30 @@
         <x:v>knowledge.program</x:v>
       </x:c>
       <x:c r="Q3" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R3" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R3" s="5" t="str">
+      <x:c r="S3" s="5" t="str">
         <x:v>Generated and uploaded Move artifacts remain workflow records; only approved evidence/facts should be published.</x:v>
       </x:c>
-      <x:c r="S3" s="5" t="str">
+      <x:c r="T3" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T3" s="5" t="str">
+      <x:c r="U3" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U3" s="5" t="str">
+      <x:c r="V3" s="5" t="str">
         <x:v>supabase/migrations/20260610170000_move_artifacts_v1.sql</x:v>
       </x:c>
-      <x:c r="V3" s="5" t="str">
+      <x:c r="W3" s="5" t="str">
         <x:v>artifact_id; tenant_id; tenant_key; move_id; phase; archetype; artifact_type; artifact_family; title; description; file_name; file_format; blob_container; blob_path; blob_sha256; file_size; version; status; generated_by; generated_at; uploaded_by; uploaded_at; source_basis; confidence</x:v>
       </x:c>
-      <x:c r="W3" s="5" t="str">
+      <x:c r="X3" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X3" s="5" t="str">
+      <x:c r="Y3" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -600,27 +610,30 @@
         <x:v>knowledge.program</x:v>
       </x:c>
       <x:c r="Q4" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R4" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R4" s="5" t="str">
+      <x:c r="S4" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S4" s="5" t="str">
+      <x:c r="T4" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T4" s="5" t="str">
+      <x:c r="U4" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U4" s="5" t="str">
+      <x:c r="V4" s="5" t="str">
         <x:v>supabase/migrations/20260523090000_client_extension_it_productivity.sql</x:v>
       </x:c>
-      <x:c r="V4" s="5" t="str">
+      <x:c r="W4" s="5" t="str">
         <x:v>id; client_id; from_move_id; to_move_id; relation_type; note; created_at; updated_at; created_by; updated_by; deleted_at</x:v>
       </x:c>
-      <x:c r="W4" s="5" t="str">
+      <x:c r="X4" s="5" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="X4" s="5" t="str">
+      <x:c r="Y4" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -672,27 +685,30 @@
         <x:v>knowledge.program</x:v>
       </x:c>
       <x:c r="Q5" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R5" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R5" s="5" t="str">
+      <x:c r="S5" s="5" t="str">
         <x:v>Workflow, review, template, or draft state remains domain-owned unless it emits accepted/published facts.</x:v>
       </x:c>
-      <x:c r="S5" s="5" t="str">
+      <x:c r="T5" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T5" s="5" t="str">
+      <x:c r="U5" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U5" s="5" t="str">
+      <x:c r="V5" s="5" t="str">
         <x:v>supabase/migrations/20260523100000_templates_data_layer.sql</x:v>
       </x:c>
-      <x:c r="V5" s="5" t="str">
+      <x:c r="W5" s="5" t="str">
         <x:v>instance_id; template_id; template_version_pinned; client_id; engagement_id; sponsor_assignments_jsonb; current_gate; status; artifact_completion_jsonb; gate_skeleton_jsonb; options_jsonb; created_by_id; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W5" s="5" t="str">
+      <x:c r="X5" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X5" s="5" t="str">
+      <x:c r="Y5" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -744,27 +760,30 @@
         <x:v>knowledge.program</x:v>
       </x:c>
       <x:c r="Q6" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R6" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R6" s="5" t="str">
+      <x:c r="S6" s="5" t="str">
         <x:v>Template content is product configuration, not enterprise Knowledge.</x:v>
       </x:c>
-      <x:c r="S6" s="5" t="str">
+      <x:c r="T6" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T6" s="5" t="str">
+      <x:c r="U6" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U6" s="5" t="str">
+      <x:c r="V6" s="5" t="str">
         <x:v>supabase/migrations/20260523100000_templates_data_layer.sql</x:v>
       </x:c>
-      <x:c r="V6" s="5" t="str">
+      <x:c r="W6" s="5" t="str">
         <x:v>id; gate_id; artifact_id; name; toc_jsonb; schema_jsonb; template_markdown; depth_score; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W6" s="5" t="str">
+      <x:c r="X6" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X6" s="5" t="str">
+      <x:c r="Y6" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -816,27 +835,30 @@
         <x:v>knowledge.program</x:v>
       </x:c>
       <x:c r="Q7" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R7" s="5" t="str">
         <x:v>archive</x:v>
       </x:c>
-      <x:c r="R7" s="5" t="str">
+      <x:c r="S7" s="5" t="str">
         <x:v>Audit/history object should be retained but not promoted as enterprise truth.</x:v>
       </x:c>
-      <x:c r="S7" s="5" t="str">
+      <x:c r="T7" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T7" s="5" t="str">
+      <x:c r="U7" s="5" t="str">
         <x:v>Archive-only; no runtime cutover.</x:v>
       </x:c>
-      <x:c r="U7" s="5" t="str">
+      <x:c r="V7" s="5" t="str">
         <x:v>supabase/migrations/20260523100000_templates_data_layer.sql</x:v>
       </x:c>
-      <x:c r="V7" s="5" t="str">
+      <x:c r="W7" s="5" t="str">
         <x:v>id; template_id; instance_id; client_id; actor_id; event_type; context_jsonb; occurred_at</x:v>
       </x:c>
-      <x:c r="W7" s="5" t="str">
+      <x:c r="X7" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X7" s="5" t="str">
+      <x:c r="Y7" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -888,27 +910,30 @@
         <x:v>knowledge.program</x:v>
       </x:c>
       <x:c r="Q8" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R8" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R8" s="5" t="str">
+      <x:c r="S8" s="5" t="str">
         <x:v>Workflow, review, template, or draft state remains domain-owned unless it emits accepted/published facts.</x:v>
       </x:c>
-      <x:c r="S8" s="5" t="str">
+      <x:c r="T8" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T8" s="5" t="str">
+      <x:c r="U8" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U8" s="5" t="str">
+      <x:c r="V8" s="5" t="str">
         <x:v>supabase/migrations/20260523100000_templates_data_layer.sql</x:v>
       </x:c>
-      <x:c r="V8" s="5" t="str">
+      <x:c r="W8" s="5" t="str">
         <x:v>id; template_id; gate_id; sequence_index; name; sponsor_raci_jsonb; required_artifacts; evidence_anchors; numeric_kill_criteria_jsonb; sensitivity_analysis_template; pre_mortem_required; time_budget_p50_days; time_budget_p90_days; hand_off_ritual; maturity_target; depth_score; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W8" s="5" t="str">
+      <x:c r="X8" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X8" s="5" t="str">
+      <x:c r="Y8" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -960,27 +985,30 @@
         <x:v>knowledge.program</x:v>
       </x:c>
       <x:c r="Q9" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R9" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R9" s="5" t="str">
+      <x:c r="S9" s="5" t="str">
         <x:v>Workflow, review, template, or draft state remains domain-owned unless it emits accepted/published facts.</x:v>
       </x:c>
-      <x:c r="S9" s="5" t="str">
+      <x:c r="T9" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T9" s="5" t="str">
+      <x:c r="U9" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U9" s="5" t="str">
+      <x:c r="V9" s="5" t="str">
         <x:v>supabase/migrations/20260523100000_templates_data_layer.sql</x:v>
       </x:c>
-      <x:c r="V9" s="5" t="str">
+      <x:c r="W9" s="5" t="str">
         <x:v>id; template_id; decision; reviewer_id; submitted_by_id; comment; depth_score; context_jsonb; created_at</x:v>
       </x:c>
-      <x:c r="W9" s="5" t="str">
+      <x:c r="X9" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X9" s="5" t="str">
+      <x:c r="Y9" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -1032,27 +1060,30 @@
         <x:v>knowledge.program</x:v>
       </x:c>
       <x:c r="Q10" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R10" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R10" s="5" t="str">
+      <x:c r="S10" s="5" t="str">
         <x:v>Workflow, review, template, or draft state remains domain-owned unless it emits accepted/published facts.</x:v>
       </x:c>
-      <x:c r="S10" s="5" t="str">
+      <x:c r="T10" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T10" s="5" t="str">
+      <x:c r="U10" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U10" s="5" t="str">
+      <x:c r="V10" s="5" t="str">
         <x:v>supabase/migrations/20260523100000_templates_data_layer.sql</x:v>
       </x:c>
-      <x:c r="V10" s="5" t="str">
+      <x:c r="W10" s="5" t="str">
         <x:v>id; template_id; version; status; snapshot_jsonb; created_by_id; created_at</x:v>
       </x:c>
-      <x:c r="W10" s="5" t="str">
+      <x:c r="X10" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X10" s="5" t="str">
+      <x:c r="Y10" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -1104,27 +1135,30 @@
         <x:v>knowledge.program</x:v>
       </x:c>
       <x:c r="Q11" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R11" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R11" s="5" t="str">
+      <x:c r="S11" s="5" t="str">
         <x:v>Workflow, review, template, or draft state remains domain-owned unless it emits accepted/published facts.</x:v>
       </x:c>
-      <x:c r="S11" s="5" t="str">
+      <x:c r="T11" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T11" s="5" t="str">
+      <x:c r="U11" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U11" s="5" t="str">
+      <x:c r="V11" s="5" t="str">
         <x:v>supabase/migrations/20260523100000_templates_data_layer.sql</x:v>
       </x:c>
-      <x:c r="V11" s="5" t="str">
+      <x:c r="W11" s="5" t="str">
         <x:v>id; slug; kind; name; summary; sponsor_raci_jsonb; version; parent_version_id; status; depth_score; published_at; retired_at; vertical_overlays; horizon_default; intended_personas; primary_author_id; approved_by_id; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W11" s="5" t="str">
+      <x:c r="X11" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X11" s="5" t="str">
+      <x:c r="Y11" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -1176,27 +1210,30 @@
         <x:v>knowledge.program</x:v>
       </x:c>
       <x:c r="Q12" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R12" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R12" s="5" t="str">
+      <x:c r="S12" s="5" t="str">
         <x:v>Workflow, review, template, or draft state remains domain-owned unless it emits accepted/published facts.</x:v>
       </x:c>
-      <x:c r="S12" s="5" t="str">
+      <x:c r="T12" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T12" s="5" t="str">
+      <x:c r="U12" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U12" s="5" t="str">
+      <x:c r="V12" s="5" t="str">
         <x:v>supabase/migrations/20260610120000_program_evidence_reviews.sql</x:v>
       </x:c>
-      <x:c r="V12" s="5" t="str">
+      <x:c r="W12" s="5" t="str">
         <x:v>id; tenant_key; program_id; evidence_id; family_key; archetype_id; phase; decision; auto_promoted; rationale; source_ref; submitted_by_user_id; reviewed_by_user_id; reviewed_at; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W12" s="5" t="str">
+      <x:c r="X12" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X12" s="5" t="str">
+      <x:c r="Y12" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -1248,27 +1285,30 @@
         <x:v>knowledge.risk_control</x:v>
       </x:c>
       <x:c r="Q13" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R13" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R13" s="5" t="str">
+      <x:c r="S13" s="5" t="str">
         <x:v>Tower source-run metadata should remain a domain registry, not canonical business truth.</x:v>
       </x:c>
-      <x:c r="S13" s="5" t="str">
+      <x:c r="T13" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T13" s="5" t="str">
+      <x:c r="U13" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U13" s="5" t="str">
+      <x:c r="V13" s="5" t="str">
         <x:v>supabase/migrations/20260616170000_ai_control_tower_substrate.sql; supabase/migrations/20260722220000_ai_control_substrate_drift_repair.sql</x:v>
       </x:c>
-      <x:c r="V13" s="5" t="str">
+      <x:c r="W13" s="5" t="str">
         <x:v>id; client_id; refresh_run_id; source_key; source_type; source_system; source_name; owner_role; cadence; data_class; period_end; refresh_status; source_fingerprint; payload; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W13" s="5" t="str">
+      <x:c r="X13" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X13" s="5" t="str">
+      <x:c r="Y13" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -1317,30 +1357,33 @@
       </x:c>
       <x:c r="O14" s="5" t="str"/>
       <x:c r="P14" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q14" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R14" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R14" s="5" t="str">
+      <x:c r="S14" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S14" s="5" t="str">
+      <x:c r="T14" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T14" s="5" t="str">
+      <x:c r="U14" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U14" s="5" t="str">
+      <x:c r="V14" s="5" t="str">
         <x:v>supabase/migrations/20260430121500_apex_setup_data_layer.sql; supabase/migrations/20260609165000_data_inventory_records_compatibility.sql</x:v>
       </x:c>
-      <x:c r="V14" s="5" t="str">
+      <x:c r="W14" s="5" t="str">
         <x:v>id; client_id; tenant_key; segment_id; record_id; title; record_kind; source_doc; source_path; source_basis; uploaded_by; uploaded_at; data_classification; confidence; last_reviewed; freshness_state; ingestion_status; indexed_at; record_text; record_payload; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W14" s="5" t="str">
+      <x:c r="X14" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X14" s="5" t="str">
+      <x:c r="Y14" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -1389,30 +1432,33 @@
       </x:c>
       <x:c r="O15" s="5" t="str"/>
       <x:c r="P15" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q15" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R15" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R15" s="5" t="str">
+      <x:c r="S15" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S15" s="5" t="str">
+      <x:c r="T15" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T15" s="5" t="str">
+      <x:c r="U15" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U15" s="5" t="str">
+      <x:c r="V15" s="5" t="str">
         <x:v>supabase/migrations/029_cross_industry_core.sql</x:v>
       </x:c>
-      <x:c r="V15" s="5" t="str">
+      <x:c r="W15" s="5" t="str">
         <x:v>id; client_id; name; source_type; storage_platform; size_tb; record_count_millions; refresh_frequency; quality_score; governance_level; data_classes; ai_ready; is_demo_data; created_at</x:v>
       </x:c>
-      <x:c r="W15" s="5" t="str">
+      <x:c r="X15" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X15" s="5" t="str">
+      <x:c r="Y15" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -1461,30 +1507,33 @@
       </x:c>
       <x:c r="O16" s="5" t="str"/>
       <x:c r="P16" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q16" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R16" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R16" s="5" t="str">
+      <x:c r="S16" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S16" s="5" t="str">
+      <x:c r="T16" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T16" s="5" t="str">
+      <x:c r="U16" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U16" s="5" t="str">
+      <x:c r="V16" s="5" t="str">
         <x:v>supabase/migrations/20260430121500_apex_setup_data_layer.sql</x:v>
       </x:c>
-      <x:c r="V16" s="5" t="str">
+      <x:c r="W16" s="5" t="str">
         <x:v>id; client_id; tenant_key; chunk_id; source_segment_id; source_record_id; source_doc; source_path; chunk_index; chunk_text; token_count; embedding_status; embedding_model; embedded_at; provenance; chunk_metadata; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W16" s="5" t="str">
+      <x:c r="X16" s="5" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="X16" s="5" t="str">
+      <x:c r="Y16" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -1533,30 +1582,33 @@
       </x:c>
       <x:c r="O17" s="5" t="str"/>
       <x:c r="P17" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q17" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R17" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R17" s="5" t="str">
+      <x:c r="S17" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S17" s="5" t="str">
+      <x:c r="T17" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T17" s="5" t="str">
+      <x:c r="U17" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U17" s="5" t="str">
+      <x:c r="V17" s="5" t="str">
         <x:v>supabase/migrations/20260514100000_enterprise_context_layer.sql</x:v>
       </x:c>
-      <x:c r="V17" s="5" t="str">
+      <x:c r="W17" s="5" t="str">
         <x:v>id; client_id; tenant_key; source_id; source_file_id; source_system; source_file; source_path; workbook_name; sheet_names; file_hash; row_count; imported_by; last_synced_at; last_validated_at; confidence; freshness_status; evidence_pointer; metadata; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W17" s="5" t="str">
+      <x:c r="X17" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X17" s="5" t="str">
+      <x:c r="Y17" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -1605,30 +1657,33 @@
       </x:c>
       <x:c r="O18" s="5" t="str"/>
       <x:c r="P18" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q18" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R18" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R18" s="5" t="str">
+      <x:c r="S18" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S18" s="5" t="str">
+      <x:c r="T18" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T18" s="5" t="str">
+      <x:c r="U18" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U18" s="5" t="str">
+      <x:c r="V18" s="5" t="str">
         <x:v>supabase/migrations/20260514100000_enterprise_context_layer.sql</x:v>
       </x:c>
-      <x:c r="V18" s="5" t="str">
+      <x:c r="W18" s="5" t="str">
         <x:v>id; client_id; tenant_key; source_system; source_key; source_type; display_name; system_of_record; source_owner; steward_owner; sync_cadence; tenant_aliases; source_status; last_synced_at; last_validated_at; confidence; freshness_status; evidence_pointer; metadata; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W18" s="5" t="str">
+      <x:c r="X18" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X18" s="5" t="str">
+      <x:c r="Y18" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -1680,27 +1735,30 @@
         <x:v>knowledge.evidence</x:v>
       </x:c>
       <x:c r="Q19" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R19" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R19" s="5" t="str">
+      <x:c r="S19" s="5" t="str">
         <x:v>Evidence-bearing object can link to canonical evidence after tenant, provenance, and review-state checks.</x:v>
       </x:c>
-      <x:c r="S19" s="5" t="str">
+      <x:c r="T19" s="5" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="T19" s="5" t="str">
+      <x:c r="U19" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U19" s="5" t="str">
+      <x:c r="V19" s="5" t="str">
         <x:v>supabase/migrations/20260421152501_intelligence_layer_core.sql</x:v>
       </x:c>
-      <x:c r="V19" s="5" t="str">
+      <x:c r="W19" s="5" t="str">
         <x:v>id; client_id; source_id; title; summary; evidence_type; related_entity_type; related_entity_id; observed_at; methodology_notes; reasoning_scope_id; disclosure_scope_id; as_of_date; confidence_level; last_verified_at; evidence_payload; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W19" s="5" t="str">
+      <x:c r="X19" s="5" t="str">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="X19" s="5" t="str">
+      <x:c r="Y19" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -1749,30 +1807,33 @@
       </x:c>
       <x:c r="O20" s="5" t="str"/>
       <x:c r="P20" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q20" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R20" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R20" s="5" t="str">
+      <x:c r="S20" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S20" s="5" t="str">
+      <x:c r="T20" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T20" s="5" t="str">
+      <x:c r="U20" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U20" s="5" t="str">
+      <x:c r="V20" s="5" t="str">
         <x:v>supabase/migrations/20260421152501_intelligence_layer_core.sql</x:v>
       </x:c>
-      <x:c r="V20" s="5" t="str">
+      <x:c r="W20" s="5" t="str">
         <x:v>id; client_id; name; description; source_tier; source_type; publisher; source_url; geography_scope; topic_scope; source_id; as_of_date; confidence_level; last_verified_at; metadata; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W20" s="5" t="str">
+      <x:c r="X20" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X20" s="5" t="str">
+      <x:c r="Y20" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -1824,27 +1885,30 @@
         <x:v>knowledge.evidence</x:v>
       </x:c>
       <x:c r="Q21" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R21" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R21" s="5" t="str">
+      <x:c r="S21" s="5" t="str">
         <x:v>Evidence-bearing object can link to canonical evidence after tenant, provenance, and review-state checks.</x:v>
       </x:c>
-      <x:c r="S21" s="5" t="str">
+      <x:c r="T21" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="T21" s="5" t="str">
+      <x:c r="U21" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U21" s="5" t="str">
+      <x:c r="V21" s="5" t="str">
         <x:v>supabase/migrations/20260721183000_home_knowledge_pack_v2.sql</x:v>
       </x:c>
-      <x:c r="V21" s="5" t="str">
+      <x:c r="W21" s="5" t="str">
         <x:v>id; pack_id; tenant_key; source_id; source_name; file_name; file_type; storage_uri; byte_size; row_count; loaded_by; loaded_at; source_date; source_owner; source_status; parsed_into_dimensions; lineage; known_gaps; source_payload; created_at</x:v>
       </x:c>
-      <x:c r="W21" s="5" t="str">
+      <x:c r="X21" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X21" s="5" t="str">
+      <x:c r="Y21" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -1893,30 +1957,33 @@
       </x:c>
       <x:c r="O22" s="5" t="str"/>
       <x:c r="P22" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q22" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R22" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R22" s="5" t="str">
+      <x:c r="S22" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S22" s="5" t="str">
+      <x:c r="T22" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T22" s="5" t="str">
+      <x:c r="U22" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U22" s="5" t="str">
+      <x:c r="V22" s="5" t="str">
         <x:v>supabase/migrations/024_knowledge_sources.sql</x:v>
       </x:c>
-      <x:c r="V22" s="5" t="str">
+      <x:c r="W22" s="5" t="str">
         <x:v>id; source_key; title; publisher; publisher_url; source_url; content_type; license_class; license_notes; industry_tags; topic_tags; published_at; half_life_days; chunk_count; pinecone_namespace; last_ingested_at; last_refresh_check_at; content_hash; status; ingestion_notes; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W22" s="5" t="str">
+      <x:c r="X22" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X22" s="5" t="str">
+      <x:c r="Y22" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -1968,27 +2035,30 @@
         <x:v>governance.tenant</x:v>
       </x:c>
       <x:c r="Q23" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R23" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R23" s="5" t="str">
+      <x:c r="S23" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S23" s="5" t="str">
+      <x:c r="T23" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T23" s="5" t="str">
+      <x:c r="U23" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U23" s="5" t="str">
+      <x:c r="V23" s="5" t="str">
         <x:v>supabase/migrations/035_user_roles.sql</x:v>
       </x:c>
-      <x:c r="V23" s="5" t="str">
+      <x:c r="W23" s="5" t="str">
         <x:v>id; person_id; client_id; role; created_at</x:v>
       </x:c>
-      <x:c r="W23" s="5" t="str">
+      <x:c r="X23" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X23" s="5" t="str">
+      <x:c r="Y23" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -2037,30 +2107,33 @@
       </x:c>
       <x:c r="O24" s="5" t="str"/>
       <x:c r="P24" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q24" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R24" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R24" s="5" t="str">
+      <x:c r="S24" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S24" s="5" t="str">
+      <x:c r="T24" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T24" s="5" t="str">
+      <x:c r="U24" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U24" s="5" t="str">
+      <x:c r="V24" s="5" t="str">
         <x:v>supabase/migrations/013_engagement_state.sql</x:v>
       </x:c>
-      <x:c r="V24" s="5" t="str">
+      <x:c r="W24" s="5" t="str">
         <x:v>id; graph_node_id; name; email; role; organization; familiarity; communication_style; working_rhythm; personal_threads; created_at; updated_at; last_seen_at</x:v>
       </x:c>
-      <x:c r="W24" s="5" t="str">
+      <x:c r="X24" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X24" s="5" t="str">
+      <x:c r="Y24" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -2112,27 +2185,30 @@
         <x:v>knowledge.evidence_acceptance</x:v>
       </x:c>
       <x:c r="Q25" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R25" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R25" s="5" t="str">
+      <x:c r="S25" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S25" s="5" t="str">
+      <x:c r="T25" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T25" s="5" t="str">
+      <x:c r="U25" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U25" s="5" t="str">
+      <x:c r="V25" s="5" t="str">
         <x:v>supabase/migrations/20260722150000_source_artifact_acceptances.sql</x:v>
       </x:c>
-      <x:c r="V25" s="5" t="str">
+      <x:c r="W25" s="5" t="str">
         <x:v>id; artifact_id; event_id; stage_key; artifact_state; authoritative_version_id; artifact_role; content_drift_status; gate_precondition_status; downstream_context_policy; diff_summary; approval_rationale; accepted_by; accepted_at; created_at</x:v>
       </x:c>
-      <x:c r="W25" s="5" t="str">
+      <x:c r="X25" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X25" s="5" t="str">
+      <x:c r="Y25" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -2184,27 +2260,30 @@
         <x:v>knowledge.evidence_chunk</x:v>
       </x:c>
       <x:c r="Q26" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R26" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R26" s="5" t="str">
+      <x:c r="S26" s="5" t="str">
         <x:v>Evidence chunks can link to canonical evidence/corpus records after provenance, citation, and retrieval checks.</x:v>
       </x:c>
-      <x:c r="S26" s="5" t="str">
+      <x:c r="T26" s="5" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="T26" s="5" t="str">
+      <x:c r="U26" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U26" s="5" t="str">
+      <x:c r="V26" s="5" t="str">
         <x:v>supabase/migrations/20260430220000_source_artifact_registry.sql</x:v>
       </x:c>
-      <x:c r="V26" s="5" t="str">
+      <x:c r="W26" s="5" t="str">
         <x:v>id; artifact_id; tenant_key; source_event_id; chunk_id; chunk_text; chunk_kind; provenance; confidence; embedding_status; created_at</x:v>
       </x:c>
-      <x:c r="W26" s="5" t="str">
+      <x:c r="X26" s="5" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="X26" s="5" t="str">
+      <x:c r="Y26" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -2256,27 +2335,30 @@
         <x:v>knowledge.fact</x:v>
       </x:c>
       <x:c r="Q27" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R27" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R27" s="5" t="str">
+      <x:c r="S27" s="5" t="str">
         <x:v>Contains enterprise-meaningful accepted, factual, commercial, metric, risk, or control data that should link through canonical IDs after review.</x:v>
       </x:c>
-      <x:c r="S27" s="5" t="str">
+      <x:c r="T27" s="5" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="T27" s="5" t="str">
+      <x:c r="U27" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U27" s="5" t="str">
+      <x:c r="V27" s="5" t="str">
         <x:v>supabase/migrations/20260430220000_source_artifact_registry.sql</x:v>
       </x:c>
-      <x:c r="V27" s="5" t="str">
+      <x:c r="W27" s="5" t="str">
         <x:v>id; artifact_id; tenant_key; source_event_id; fact_type; fact_key; fact_value; provenance; confidence; validation_status; created_at</x:v>
       </x:c>
-      <x:c r="W27" s="5" t="str">
+      <x:c r="X27" s="5" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="X27" s="5" t="str">
+      <x:c r="Y27" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -2328,27 +2410,30 @@
         <x:v>knowledge.evidence</x:v>
       </x:c>
       <x:c r="Q28" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R28" s="5" t="str">
         <x:v>archive</x:v>
       </x:c>
-      <x:c r="R28" s="5" t="str">
+      <x:c r="S28" s="5" t="str">
         <x:v>Audit/history object should be retained but not promoted as enterprise truth.</x:v>
       </x:c>
-      <x:c r="S28" s="5" t="str">
+      <x:c r="T28" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T28" s="5" t="str">
+      <x:c r="U28" s="5" t="str">
         <x:v>Archive-only; no runtime cutover.</x:v>
       </x:c>
-      <x:c r="U28" s="5" t="str">
+      <x:c r="V28" s="5" t="str">
         <x:v>supabase/migrations/20260616234000_source_artifact_generation_jobs.sql</x:v>
       </x:c>
-      <x:c r="V28" s="5" t="str">
+      <x:c r="W28" s="5" t="str">
         <x:v>id; client_key; source_event_id; artifact_row_id; artifact_code; stage_key; status; quality_tier; requested_via; requested_by_user_id; attempt_count; max_attempts; locked_by; locked_at; started_at; completed_at; last_error; result_metadata; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W28" s="5" t="str">
+      <x:c r="X28" s="5" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="X28" s="5" t="str">
+      <x:c r="Y28" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -2400,27 +2485,30 @@
         <x:v>knowledge.evidence</x:v>
       </x:c>
       <x:c r="Q29" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R29" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R29" s="5" t="str">
+      <x:c r="S29" s="5" t="str">
         <x:v>Source owns uploaded/generated artifact lifecycle; extracted facts/evidence publish separately.</x:v>
       </x:c>
-      <x:c r="S29" s="5" t="str">
+      <x:c r="T29" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T29" s="5" t="str">
+      <x:c r="U29" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U29" s="5" t="str">
+      <x:c r="V29" s="5" t="str">
         <x:v>supabase/migrations/20260430220000_source_artifact_registry.sql; supabase/migrations/20260610203000_source_artifacts.sql</x:v>
       </x:c>
-      <x:c r="V29" s="5" t="str">
+      <x:c r="W29" s="5" t="str">
         <x:v>id; tenant_key; source_event_id; source_event_row_id; stage_key; artifact_family; artifact_kind; source_origin; source_format; original_name; blob_uri; uploader_user_id; mime_type; size_bytes; sha256; parse_status; embedding_status; graph_status; classification_status; data_classification; evidence_state; approval_state; version; supersedes_artifact_version_id</x:v>
       </x:c>
-      <x:c r="W29" s="5" t="str">
+      <x:c r="X29" s="5" t="str">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="X29" s="5" t="str">
+      <x:c r="Y29" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -2469,30 +2557,33 @@
       </x:c>
       <x:c r="O30" s="5" t="str"/>
       <x:c r="P30" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q30" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R30" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R30" s="5" t="str">
+      <x:c r="S30" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S30" s="5" t="str">
+      <x:c r="T30" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T30" s="5" t="str">
+      <x:c r="U30" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U30" s="5" t="str">
+      <x:c r="V30" s="5" t="str">
         <x:v>supabase/migrations/20260430220000_source_artifact_registry.sql</x:v>
       </x:c>
-      <x:c r="V30" s="5" t="str">
+      <x:c r="W30" s="5" t="str">
         <x:v>id; artifact_id; tenant_key; source_event_id; vendor_id; exception_type; severity; description; recommendation; provenance; status; confidence; created_at</x:v>
       </x:c>
-      <x:c r="W30" s="5" t="str">
+      <x:c r="X30" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X30" s="5" t="str">
+      <x:c r="Y30" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -2541,30 +2632,33 @@
       </x:c>
       <x:c r="O31" s="5" t="str"/>
       <x:c r="P31" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q31" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R31" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R31" s="5" t="str">
+      <x:c r="S31" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S31" s="5" t="str">
+      <x:c r="T31" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T31" s="5" t="str">
+      <x:c r="U31" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U31" s="5" t="str">
+      <x:c r="V31" s="5" t="str">
         <x:v>supabase/migrations/20260430220000_source_artifact_registry.sql</x:v>
       </x:c>
-      <x:c r="V31" s="5" t="str">
+      <x:c r="W31" s="5" t="str">
         <x:v>id; tenant_key; source_event_id; turn_id; agent_name; question; used_artifact_ids; used_chunk_ids; used_fact_ids; used_graph_edge_ids; used_pattern_ids; created_at</x:v>
       </x:c>
-      <x:c r="W31" s="5" t="str">
+      <x:c r="X31" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X31" s="5" t="str">
+      <x:c r="Y31" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -2613,30 +2707,33 @@
       </x:c>
       <x:c r="O32" s="5" t="str"/>
       <x:c r="P32" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
+        <x:v>knowledge.evidence_manifest</x:v>
       </x:c>
       <x:c r="Q32" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R32" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R32" s="5" t="str">
+      <x:c r="S32" s="5" t="str">
         <x:v>Contains enterprise-meaningful accepted, factual, commercial, metric, risk, or control data that should link through canonical IDs after review.</x:v>
       </x:c>
-      <x:c r="S32" s="5" t="str">
+      <x:c r="T32" s="5" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="T32" s="5" t="str">
+      <x:c r="U32" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U32" s="5" t="str">
+      <x:c r="V32" s="5" t="str">
         <x:v>supabase/migrations/20260704193000_source_contract_evidence_persistence.sql</x:v>
       </x:c>
-      <x:c r="V32" s="5" t="str">
+      <x:c r="W32" s="5" t="str">
         <x:v>id; tenant_key; source_event_id; source_artifact_id; archetype_key; evidence_pack_name; upload_batch_id; source_type; validation_status; row_count; required_family_count; covered_required_family_count; missing_required_families; warnings; metadata; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W32" s="5" t="str">
+      <x:c r="X32" s="5" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="X32" s="5" t="str">
+      <x:c r="Y32" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -2687,30 +2784,33 @@
         <x:v>Metric/value/cost family candidate</x:v>
       </x:c>
       <x:c r="P33" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
+        <x:v>knowledge.metric_observation</x:v>
       </x:c>
       <x:c r="Q33" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R33" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R33" s="5" t="str">
+      <x:c r="S33" s="5" t="str">
         <x:v>Contains enterprise-meaningful accepted, factual, commercial, metric, risk, or control data that should link through canonical IDs after review.</x:v>
       </x:c>
-      <x:c r="S33" s="5" t="str">
+      <x:c r="T33" s="5" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="T33" s="5" t="str">
+      <x:c r="U33" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U33" s="5" t="str">
+      <x:c r="V33" s="5" t="str">
         <x:v>supabase/migrations/20260704193000_source_contract_evidence_persistence.sql</x:v>
       </x:c>
-      <x:c r="V33" s="5" t="str">
+      <x:c r="W33" s="5" t="str">
         <x:v>id; manifest_id; tenant_key; source_event_id; archetype_key; metric_key; metric_label; metric_value; unit; evidence_family; basis; confidence; validation_status; created_at</x:v>
       </x:c>
-      <x:c r="W33" s="5" t="str">
+      <x:c r="X33" s="5" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="X33" s="5" t="str">
+      <x:c r="Y33" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -2759,30 +2859,33 @@
       </x:c>
       <x:c r="O34" s="5" t="str"/>
       <x:c r="P34" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
+        <x:v>knowledge.evidence_fragment_or_contract_fact_assertion</x:v>
       </x:c>
       <x:c r="Q34" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R34" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R34" s="5" t="str">
+      <x:c r="S34" s="5" t="str">
         <x:v>Contains enterprise-meaningful accepted, factual, commercial, metric, risk, or control data that should link through canonical IDs after review.</x:v>
       </x:c>
-      <x:c r="S34" s="5" t="str">
+      <x:c r="T34" s="5" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="T34" s="5" t="str">
+      <x:c r="U34" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U34" s="5" t="str">
+      <x:c r="V34" s="5" t="str">
         <x:v>supabase/migrations/20260704193000_source_contract_evidence_persistence.sql</x:v>
       </x:c>
-      <x:c r="V34" s="5" t="str">
+      <x:c r="W34" s="5" t="str">
         <x:v>id; manifest_id; tenant_key; source_event_id; source_artifact_id; archetype_key; evidence_family; source_sheet; source_row_number; row_hash; row_payload; normalized_subject; period_start; period_end; amount_usd; confidence; validation_status; created_at</x:v>
       </x:c>
-      <x:c r="W34" s="5" t="str">
+      <x:c r="X34" s="5" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="X34" s="5" t="str">
+      <x:c r="Y34" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -2831,30 +2934,33 @@
       </x:c>
       <x:c r="O35" s="5" t="str"/>
       <x:c r="P35" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
+        <x:v>knowledge.contract_finding</x:v>
       </x:c>
       <x:c r="Q35" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R35" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R35" s="5" t="str">
+      <x:c r="S35" s="5" t="str">
         <x:v>Contains enterprise-meaningful accepted, factual, commercial, metric, risk, or control data that should link through canonical IDs after review.</x:v>
       </x:c>
-      <x:c r="S35" s="5" t="str">
+      <x:c r="T35" s="5" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="T35" s="5" t="str">
+      <x:c r="U35" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U35" s="5" t="str">
+      <x:c r="V35" s="5" t="str">
         <x:v>supabase/migrations/20260701120000_source_contract_optimization_mve.sql</x:v>
       </x:c>
-      <x:c r="V35" s="5" t="str">
+      <x:c r="W35" s="5" t="str">
         <x:v>id; profile_id; tenant_key; source_event_id; finding_key; category; severity; title; current_state; sourcing_implication; recommended_action; estimated_annual_impact_usd; confidence; evidence_refs; created_at</x:v>
       </x:c>
-      <x:c r="W35" s="5" t="str">
+      <x:c r="X35" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X35" s="5" t="str">
+      <x:c r="Y35" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -2903,30 +3009,33 @@
       </x:c>
       <x:c r="O36" s="5" t="str"/>
       <x:c r="P36" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
+        <x:v>knowledge.value_driver_or_commercial_lever</x:v>
       </x:c>
       <x:c r="Q36" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R36" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R36" s="5" t="str">
+      <x:c r="S36" s="5" t="str">
         <x:v>Contains enterprise-meaningful accepted, factual, commercial, metric, risk, or control data that should link through canonical IDs after review.</x:v>
       </x:c>
-      <x:c r="S36" s="5" t="str">
+      <x:c r="T36" s="5" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="T36" s="5" t="str">
+      <x:c r="U36" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U36" s="5" t="str">
+      <x:c r="V36" s="5" t="str">
         <x:v>supabase/migrations/20260701120000_source_contract_optimization_mve.sql</x:v>
       </x:c>
-      <x:c r="V36" s="5" t="str">
+      <x:c r="W36" s="5" t="str">
         <x:v>id; profile_id; tenant_key; source_event_id; lever_key; lever_type; finding_key; priority; buyer_ask; negotiation_language; value_basis; annual_impact_low_usd; annual_impact_high_usd; owner_role; created_at</x:v>
       </x:c>
-      <x:c r="W36" s="5" t="str">
+      <x:c r="X36" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X36" s="5" t="str">
+      <x:c r="Y36" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -2975,30 +3084,33 @@
       </x:c>
       <x:c r="O37" s="5" t="str"/>
       <x:c r="P37" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
+        <x:v>knowledge.contract_profile</x:v>
       </x:c>
       <x:c r="Q37" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R37" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R37" s="5" t="str">
+      <x:c r="S37" s="5" t="str">
         <x:v>Contains enterprise-meaningful accepted, factual, commercial, metric, risk, or control data that should link through canonical IDs after review.</x:v>
       </x:c>
-      <x:c r="S37" s="5" t="str">
+      <x:c r="T37" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="T37" s="5" t="str">
+      <x:c r="U37" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U37" s="5" t="str">
+      <x:c r="V37" s="5" t="str">
         <x:v>supabase/migrations/20260701120000_source_contract_optimization_mve.sql</x:v>
       </x:c>
-      <x:c r="V37" s="5" t="str">
+      <x:c r="W37" s="5" t="str">
         <x:v>id; tenant_key; source_event_id; incumbent_vendor_id; incumbent_vendor_name; contract_name; source_type; synthetic_demo; decision_use; current_annual_run_rate_usd; term_start; term_end; renewal_notice_date; ready_for_optimization; ready_reason; extraction_boundary; profile_payload; evidence_artifact_ids; evidence_refs; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W37" s="5" t="str">
+      <x:c r="X37" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X37" s="5" t="str">
+      <x:c r="Y37" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -3047,30 +3159,33 @@
       </x:c>
       <x:c r="O38" s="5" t="str"/>
       <x:c r="P38" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q38" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R38" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R38" s="5" t="str">
+      <x:c r="S38" s="5" t="str">
         <x:v>Workflow, review, template, or draft state remains domain-owned unless it emits accepted/published facts.</x:v>
       </x:c>
-      <x:c r="S38" s="5" t="str">
+      <x:c r="T38" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T38" s="5" t="str">
+      <x:c r="U38" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U38" s="5" t="str">
+      <x:c r="V38" s="5" t="str">
         <x:v>supabase/migrations/20260602113000_source_event_activity.sql</x:v>
       </x:c>
-      <x:c r="V38" s="5" t="str">
+      <x:c r="W38" s="5" t="str">
         <x:v>id; event_id; client_key; actor_user_id; actor_display_name; actor_role; action_type; action_label; stage_key; artifact_code; criterion_id; reason; metadata; occurred_at; created_at</x:v>
       </x:c>
-      <x:c r="W38" s="5" t="str">
+      <x:c r="X38" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X38" s="5" t="str">
+      <x:c r="Y38" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -3122,27 +3237,30 @@
         <x:v>knowledge.application</x:v>
       </x:c>
       <x:c r="Q39" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R39" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R39" s="5" t="str">
+      <x:c r="S39" s="5" t="str">
         <x:v>Workflow, review, template, or draft state remains domain-owned unless it emits accepted/published facts.</x:v>
       </x:c>
-      <x:c r="S39" s="5" t="str">
+      <x:c r="T39" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T39" s="5" t="str">
+      <x:c r="U39" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U39" s="5" t="str">
+      <x:c r="V39" s="5" t="str">
         <x:v>supabase/migrations/20260430151000_source_event_approvals.sql</x:v>
       </x:c>
-      <x:c r="V39" s="5" t="str">
+      <x:c r="W39" s="5" t="str">
         <x:v>id; event_id; action; approved_by_user_id; from_state; to_state; notes; approved_at</x:v>
       </x:c>
-      <x:c r="W39" s="5" t="str">
+      <x:c r="X39" s="5" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="X39" s="5" t="str">
+      <x:c r="Y39" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -3194,27 +3312,30 @@
         <x:v>knowledge.evidence</x:v>
       </x:c>
       <x:c r="Q40" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R40" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R40" s="5" t="str">
+      <x:c r="S40" s="5" t="str">
         <x:v>Artifact readiness state belongs to Source workflow; linked artifacts/facts publish separately.</x:v>
       </x:c>
-      <x:c r="S40" s="5" t="str">
+      <x:c r="T40" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T40" s="5" t="str">
+      <x:c r="U40" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U40" s="5" t="str">
+      <x:c r="V40" s="5" t="str">
         <x:v>supabase/migrations/20260507230000_source_canvas_per_event_substrate.sql</x:v>
       </x:c>
-      <x:c r="V40" s="5" t="str">
+      <x:c r="W40" s="5" t="str">
         <x:v>id; source_event_id; tenant_key; artifact_code; stage_key; artifact_family; tier; status; requirement_level; gate_defining; linked_artifact_id; notes; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W40" s="5" t="str">
+      <x:c r="X40" s="5" t="str">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="X40" s="5" t="str">
+      <x:c r="Y40" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -3263,30 +3384,33 @@
       </x:c>
       <x:c r="O41" s="5" t="str"/>
       <x:c r="P41" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q41" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R41" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R41" s="5" t="str">
+      <x:c r="S41" s="5" t="str">
         <x:v>Workflow, review, template, or draft state remains domain-owned unless it emits accepted/published facts.</x:v>
       </x:c>
-      <x:c r="S41" s="5" t="str">
+      <x:c r="T41" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T41" s="5" t="str">
+      <x:c r="U41" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U41" s="5" t="str">
+      <x:c r="V41" s="5" t="str">
         <x:v>supabase/migrations/20260524170000_decision_dossier_v1.sql</x:v>
       </x:c>
-      <x:c r="V41" s="5" t="str">
+      <x:c r="W41" s="5" t="str">
         <x:v>id; source_event_id; client_key; old_code; new_code; actor; reason; occurred_at</x:v>
       </x:c>
-      <x:c r="W41" s="5" t="str">
+      <x:c r="X41" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X41" s="5" t="str">
+      <x:c r="Y41" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -3338,27 +3462,30 @@
         <x:v>knowledge.evidence</x:v>
       </x:c>
       <x:c r="Q42" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R42" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R42" s="5" t="str">
+      <x:c r="S42" s="5" t="str">
         <x:v>Workflow, review, template, or draft state remains domain-owned unless it emits accepted/published facts.</x:v>
       </x:c>
-      <x:c r="S42" s="5" t="str">
+      <x:c r="T42" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T42" s="5" t="str">
+      <x:c r="U42" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U42" s="5" t="str">
+      <x:c r="V42" s="5" t="str">
         <x:v>supabase/migrations/20260507230000_source_canvas_per_event_substrate.sql</x:v>
       </x:c>
-      <x:c r="V42" s="5" t="str">
+      <x:c r="W42" s="5" t="str">
         <x:v>id; source_event_id; tenant_key; requirement_id; stage_key; current_state; source_artifact_id; notes; last_synced_at; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W42" s="5" t="str">
+      <x:c r="X42" s="5" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="X42" s="5" t="str">
+      <x:c r="Y42" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -3410,27 +3537,30 @@
         <x:v>knowledge.fact</x:v>
       </x:c>
       <x:c r="Q43" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R43" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R43" s="5" t="str">
+      <x:c r="S43" s="5" t="str">
         <x:v>Contains enterprise-meaningful accepted, factual, commercial, metric, risk, or control data that should link through canonical IDs after review.</x:v>
       </x:c>
-      <x:c r="S43" s="5" t="str">
+      <x:c r="T43" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="T43" s="5" t="str">
+      <x:c r="U43" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U43" s="5" t="str">
+      <x:c r="V43" s="5" t="str">
         <x:v>supabase/migrations/20260706120000_source_event_facts.sql</x:v>
       </x:c>
-      <x:c r="V43" s="5" t="str">
+      <x:c r="W43" s="5" t="str">
         <x:v>id; source_event_id; client_key; fact_key; entity_kind; entity_ref; value_numeric; value_text; unit; source_method; source_citation; confidence; captured_at; is_stale</x:v>
       </x:c>
-      <x:c r="W43" s="5" t="str">
+      <x:c r="X43" s="5" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="X43" s="5" t="str">
+      <x:c r="Y43" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -3479,30 +3609,33 @@
       </x:c>
       <x:c r="O44" s="5" t="str"/>
       <x:c r="P44" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q44" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R44" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R44" s="5" t="str">
+      <x:c r="S44" s="5" t="str">
         <x:v>Workflow, review, template, or draft state remains domain-owned unless it emits accepted/published facts.</x:v>
       </x:c>
-      <x:c r="S44" s="5" t="str">
+      <x:c r="T44" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T44" s="5" t="str">
+      <x:c r="U44" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U44" s="5" t="str">
+      <x:c r="V44" s="5" t="str">
         <x:v>supabase/migrations/20260507230000_source_canvas_per_event_substrate.sql</x:v>
       </x:c>
-      <x:c r="V44" s="5" t="str">
+      <x:c r="W44" s="5" t="str">
         <x:v>id; source_event_id; tenant_key; criterion_id; from_stage; to_stage; state; reviewer_user_id; reviewed_at; notes; evidence_artifact_ids; waiver_approval_id; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W44" s="5" t="str">
+      <x:c r="X44" s="5" t="str">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="X44" s="5" t="str">
+      <x:c r="Y44" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -3551,30 +3684,33 @@
       </x:c>
       <x:c r="O45" s="5" t="str"/>
       <x:c r="P45" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q45" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R45" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R45" s="5" t="str">
+      <x:c r="S45" s="5" t="str">
         <x:v>Workflow, review, template, or draft state remains domain-owned unless it emits accepted/published facts.</x:v>
       </x:c>
-      <x:c r="S45" s="5" t="str">
+      <x:c r="T45" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T45" s="5" t="str">
+      <x:c r="U45" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U45" s="5" t="str">
+      <x:c r="V45" s="5" t="str">
         <x:v>supabase/migrations/20260501170000_source_access_control.sql</x:v>
       </x:c>
-      <x:c r="V45" s="5" t="str">
+      <x:c r="W45" s="5" t="str">
         <x:v>id; client_key; source_event_id; source_event_row_id; user_id; user_name; role; approval_authority; source_access_level; can_view_financial; can_upload_source_artifacts; can_generate_sourcing_artifacts; can_publish_sourcing_artifacts; can_approve_source_stages; can_approve_award; notify_on; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W45" s="5" t="str">
+      <x:c r="X45" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X45" s="5" t="str">
+      <x:c r="Y45" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -3623,30 +3759,33 @@
       </x:c>
       <x:c r="O46" s="5" t="str"/>
       <x:c r="P46" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q46" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R46" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R46" s="5" t="str">
+      <x:c r="S46" s="5" t="str">
         <x:v>Workflow, review, template, or draft state remains domain-owned unless it emits accepted/published facts.</x:v>
       </x:c>
-      <x:c r="S46" s="5" t="str">
+      <x:c r="T46" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T46" s="5" t="str">
+      <x:c r="U46" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U46" s="5" t="str">
+      <x:c r="V46" s="5" t="str">
         <x:v>supabase/migrations/20260508040000_source_event_pricing_submissions.sql</x:v>
       </x:c>
-      <x:c r="V46" s="5" t="str">
+      <x:c r="W46" s="5" t="str">
         <x:v>id; source_event_id; tenant_key; vendor_name; submitted_at; uploaded_by_user_id; uploaded_filename; unit_prices_by_id; vendor_notes_by_id; pricing_notes; assumption_deviations; parse_status; parse_warnings; superseded_by; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W46" s="5" t="str">
+      <x:c r="X46" s="5" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="X46" s="5" t="str">
+      <x:c r="Y46" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -3695,30 +3834,33 @@
       </x:c>
       <x:c r="O47" s="5" t="str"/>
       <x:c r="P47" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q47" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R47" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R47" s="5" t="str">
+      <x:c r="S47" s="5" t="str">
         <x:v>Workflow, review, template, or draft state remains domain-owned unless it emits accepted/published facts.</x:v>
       </x:c>
-      <x:c r="S47" s="5" t="str">
+      <x:c r="T47" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T47" s="5" t="str">
+      <x:c r="U47" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U47" s="5" t="str">
+      <x:c r="V47" s="5" t="str">
         <x:v>supabase/migrations/20260430150000_source_events.sql</x:v>
       </x:c>
-      <x:c r="V47" s="5" t="str">
+      <x:c r="W47" s="5" t="str">
         <x:v>id; client_key; event_code; event_name; event_type; current_stage_key; lifecycle_state; linked_program_id; estimated_value_usd; trigger_description; scope_description; decision_owner; created_by_user_id; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W47" s="5" t="str">
+      <x:c r="X47" s="5" t="str">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="X47" s="5" t="str">
+      <x:c r="Y47" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -3767,30 +3909,33 @@
       </x:c>
       <x:c r="O48" s="5" t="str"/>
       <x:c r="P48" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q48" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R48" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R48" s="5" t="str">
+      <x:c r="S48" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S48" s="5" t="str">
+      <x:c r="T48" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T48" s="5" t="str">
+      <x:c r="U48" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U48" s="5" t="str">
+      <x:c r="V48" s="5" t="str">
         <x:v>supabase/migrations/20260430220000_source_artifact_registry.sql</x:v>
       </x:c>
-      <x:c r="V48" s="5" t="str">
+      <x:c r="W48" s="5" t="str">
         <x:v>id; artifact_id; tenant_key; source_event_id; from_node_id; edge_type; to_node_id; provenance; confidence; graph_status; created_at</x:v>
       </x:c>
-      <x:c r="W48" s="5" t="str">
+      <x:c r="X48" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X48" s="5" t="str">
+      <x:c r="Y48" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -3841,30 +3986,33 @@
         <x:v>Metric/value/cost family candidate</x:v>
       </x:c>
       <x:c r="P49" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q49" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R49" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R49" s="5" t="str">
+      <x:c r="S49" s="5" t="str">
         <x:v>Contains enterprise-meaningful accepted, factual, commercial, metric, risk, or control data that should link through canonical IDs after review.</x:v>
       </x:c>
-      <x:c r="S49" s="5" t="str">
+      <x:c r="T49" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="T49" s="5" t="str">
+      <x:c r="U49" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U49" s="5" t="str">
+      <x:c r="V49" s="5" t="str">
         <x:v>supabase/migrations/20260430220000_source_artifact_registry.sql</x:v>
       </x:c>
-      <x:c r="V49" s="5" t="str">
+      <x:c r="W49" s="5" t="str">
         <x:v>id; artifact_id; tenant_key; source_event_id; outcome_type; outcome_text; owner; due_date; status; provenance; confidence; created_at</x:v>
       </x:c>
-      <x:c r="W49" s="5" t="str">
+      <x:c r="X49" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X49" s="5" t="str">
+      <x:c r="Y49" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -3913,30 +4061,33 @@
       </x:c>
       <x:c r="O50" s="5" t="str"/>
       <x:c r="P50" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q50" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R50" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R50" s="5" t="str">
+      <x:c r="S50" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S50" s="5" t="str">
+      <x:c r="T50" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T50" s="5" t="str">
+      <x:c r="U50" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U50" s="5" t="str">
+      <x:c r="V50" s="5" t="str">
         <x:v>supabase/migrations/20260430220000_source_artifact_registry.sql</x:v>
       </x:c>
-      <x:c r="V50" s="5" t="str">
+      <x:c r="W50" s="5" t="str">
         <x:v>id; artifact_id; tenant_key; source_event_id; vendor_id; component_key; component_label; amount_usd; unit; year_index; pricing_model; assumptions; provenance; confidence; created_at</x:v>
       </x:c>
-      <x:c r="W50" s="5" t="str">
+      <x:c r="X50" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X50" s="5" t="str">
+      <x:c r="Y50" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -3985,30 +4136,33 @@
       </x:c>
       <x:c r="O51" s="5" t="str"/>
       <x:c r="P51" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q51" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R51" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R51" s="5" t="str">
+      <x:c r="S51" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S51" s="5" t="str">
+      <x:c r="T51" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T51" s="5" t="str">
+      <x:c r="U51" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U51" s="5" t="str">
+      <x:c r="V51" s="5" t="str">
         <x:v>supabase/migrations/20260620000000_source_reasoning_envelopes.sql</x:v>
       </x:c>
-      <x:c r="V51" s="5" t="str">
+      <x:c r="W51" s="5" t="str">
         <x:v>id; envelope_id; source_event_id; artifact_code; tenant_key; stage; status; archetype; rigor; confidence_label; confidence_score; refusal_reason; missing_evidence; claims; envelope; generated_by_user_id; generated_at; created_at</x:v>
       </x:c>
-      <x:c r="W51" s="5" t="str">
+      <x:c r="X51" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X51" s="5" t="str">
+      <x:c r="Y51" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -4057,30 +4211,33 @@
       </x:c>
       <x:c r="O52" s="5" t="str"/>
       <x:c r="P52" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q52" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R52" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R52" s="5" t="str">
+      <x:c r="S52" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S52" s="5" t="str">
+      <x:c r="T52" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T52" s="5" t="str">
+      <x:c r="U52" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U52" s="5" t="str">
+      <x:c r="V52" s="5" t="str">
         <x:v>supabase/migrations/20260430220000_source_artifact_registry.sql</x:v>
       </x:c>
-      <x:c r="V52" s="5" t="str">
+      <x:c r="W52" s="5" t="str">
         <x:v>id; artifact_id; tenant_key; source_event_id; requirement_key; requirement_text; requirement_category; required; provenance; confidence; created_at</x:v>
       </x:c>
-      <x:c r="W52" s="5" t="str">
+      <x:c r="X52" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X52" s="5" t="str">
+      <x:c r="Y52" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -4129,30 +4286,33 @@
       </x:c>
       <x:c r="O53" s="5" t="str"/>
       <x:c r="P53" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q53" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R53" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R53" s="5" t="str">
+      <x:c r="S53" s="5" t="str">
         <x:v>Workflow, review, template, or draft state remains domain-owned unless it emits accepted/published facts.</x:v>
       </x:c>
-      <x:c r="S53" s="5" t="str">
+      <x:c r="T53" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T53" s="5" t="str">
+      <x:c r="U53" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U53" s="5" t="str">
+      <x:c r="V53" s="5" t="str">
         <x:v>supabase/migrations/20260720130000_source_stage_guidebooks.sql</x:v>
       </x:c>
-      <x:c r="V53" s="5" t="str">
+      <x:c r="W53" s="5" t="str">
         <x:v>id; stage_key; client_key; title; purpose; duration_minutes; status; sections; version; created_by; updated_by; published_at; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W53" s="5" t="str">
+      <x:c r="X53" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X53" s="5" t="str">
+      <x:c r="Y53" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -4203,30 +4363,33 @@
         <x:v>Metric/value/cost family candidate</x:v>
       </x:c>
       <x:c r="P54" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
+        <x:v>knowledge.value_flow_step</x:v>
       </x:c>
       <x:c r="Q54" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R54" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R54" s="5" t="str">
+      <x:c r="S54" s="5" t="str">
         <x:v>Contains enterprise-meaningful accepted, factual, commercial, metric, risk, or control data that should link through canonical IDs after review.</x:v>
       </x:c>
-      <x:c r="S54" s="5" t="str">
+      <x:c r="T54" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="T54" s="5" t="str">
+      <x:c r="U54" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U54" s="5" t="str">
+      <x:c r="V54" s="5" t="str">
         <x:v>supabase/migrations/20260524173000_source_value_proof_loop_v1.sql</x:v>
       </x:c>
-      <x:c r="V54" s="5" t="str">
+      <x:c r="W54" s="5" t="str">
         <x:v>id; source_event_id; chain_step; state_id; delta_from_prior_usd; delta_classification; created_at</x:v>
       </x:c>
-      <x:c r="W54" s="5" t="str">
+      <x:c r="X54" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X54" s="5" t="str">
+      <x:c r="Y54" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -4277,30 +4440,33 @@
         <x:v>Metric/value/cost family candidate</x:v>
       </x:c>
       <x:c r="P55" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
+        <x:v>knowledge.value_driver_or_lever</x:v>
       </x:c>
       <x:c r="Q55" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R55" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R55" s="5" t="str">
+      <x:c r="S55" s="5" t="str">
         <x:v>Contains enterprise-meaningful accepted, factual, commercial, metric, risk, or control data that should link through canonical IDs after review.</x:v>
       </x:c>
-      <x:c r="S55" s="5" t="str">
+      <x:c r="T55" s="5" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="T55" s="5" t="str">
+      <x:c r="U55" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U55" s="5" t="str">
+      <x:c r="V55" s="5" t="str">
         <x:v>supabase/migrations/20260706160000_source_value_levers.sql</x:v>
       </x:c>
-      <x:c r="V55" s="5" t="str">
+      <x:c r="W55" s="5" t="str">
         <x:v>id; source_event_id; client_key; lever_key; lever_name; value_type; formula_id; est_low_usd; est_high_usd; confidence; basis; derivation_trace; evidence_refs; insufficient_evidence; missing_evidence; computed_at; AND</x:v>
       </x:c>
-      <x:c r="W55" s="5" t="str">
+      <x:c r="X55" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X55" s="5" t="str">
+      <x:c r="Y55" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -4351,30 +4517,33 @@
         <x:v>Metric/value/cost family candidate</x:v>
       </x:c>
       <x:c r="P56" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q56" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R56" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R56" s="5" t="str">
+      <x:c r="S56" s="5" t="str">
         <x:v>Contains enterprise-meaningful accepted, factual, commercial, metric, risk, or control data that should link through canonical IDs after review.</x:v>
       </x:c>
-      <x:c r="S56" s="5" t="str">
+      <x:c r="T56" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="T56" s="5" t="str">
+      <x:c r="U56" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U56" s="5" t="str">
+      <x:c r="V56" s="5" t="str">
         <x:v>supabase/migrations/20260507220000_source_value_lines.sql</x:v>
       </x:c>
-      <x:c r="V56" s="5" t="str">
+      <x:c r="W56" s="5" t="str">
         <x:v>id; program_id; label; category; value_state; projected_amount; committed_amount; realized_amount; value_unit; measurement_owner_id; evidence_artifact_id; notes; sort_order; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W56" s="5" t="str">
+      <x:c r="X56" s="5" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="X56" s="5" t="str">
+      <x:c r="Y56" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -4425,30 +4594,33 @@
         <x:v>Metric/value/cost family candidate</x:v>
       </x:c>
       <x:c r="P57" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
+        <x:v>knowledge.value_state_or_readiness</x:v>
       </x:c>
       <x:c r="Q57" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R57" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R57" s="5" t="str">
+      <x:c r="S57" s="5" t="str">
         <x:v>Contains enterprise-meaningful accepted, factual, commercial, metric, risk, or control data that should link through canonical IDs after review.</x:v>
       </x:c>
-      <x:c r="S57" s="5" t="str">
+      <x:c r="T57" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="T57" s="5" t="str">
+      <x:c r="U57" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U57" s="5" t="str">
+      <x:c r="V57" s="5" t="str">
         <x:v>supabase/migrations/20260524173000_source_value_proof_loop_v1.sql</x:v>
       </x:c>
-      <x:c r="V57" s="5" t="str">
+      <x:c r="W57" s="5" t="str">
         <x:v>id; client_id; source_event_id; state_layer; state_subtype; amount_usd; amount_basis; methodology; evidence_ledger_ids; state_date; attested_by; attested_at; attestation_audit_id; superseded_by; created_at; created_by; OR</x:v>
       </x:c>
-      <x:c r="W57" s="5" t="str">
+      <x:c r="X57" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X57" s="5" t="str">
+      <x:c r="Y57" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -4497,30 +4669,33 @@
       </x:c>
       <x:c r="O58" s="5" t="str"/>
       <x:c r="P58" s="5" t="str">
-        <x:v>knowledge.vendor</x:v>
+        <x:v>knowledge.commercial_commitment</x:v>
       </x:c>
       <x:c r="Q58" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R58" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R58" s="5" t="str">
+      <x:c r="S58" s="5" t="str">
         <x:v>Contains enterprise-meaningful accepted, factual, commercial, metric, risk, or control data that should link through canonical IDs after review.</x:v>
       </x:c>
-      <x:c r="S58" s="5" t="str">
+      <x:c r="T58" s="5" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="T58" s="5" t="str">
+      <x:c r="U58" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U58" s="5" t="str">
+      <x:c r="V58" s="5" t="str">
         <x:v>supabase/migrations/20260430220000_source_artifact_registry.sql</x:v>
       </x:c>
-      <x:c r="V58" s="5" t="str">
+      <x:c r="W58" s="5" t="str">
         <x:v>id; artifact_id; tenant_key; source_event_id; vendor_id; commitment_type; commitment_text; metric; provenance; confidence; created_at</x:v>
       </x:c>
-      <x:c r="W58" s="5" t="str">
+      <x:c r="X58" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X58" s="5" t="str">
+      <x:c r="Y58" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -4572,27 +4747,30 @@
         <x:v>governance.review_state</x:v>
       </x:c>
       <x:c r="Q59" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R59" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R59" s="5" t="str">
+      <x:c r="S59" s="5" t="str">
         <x:v>Review status for extracted proposal facts stays operational; approved facts publish separately.</x:v>
       </x:c>
-      <x:c r="S59" s="5" t="str">
+      <x:c r="T59" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T59" s="5" t="str">
+      <x:c r="U59" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U59" s="5" t="str">
+      <x:c r="V59" s="5" t="str">
         <x:v>supabase/migrations/20260725190000_source_vendor_proposal_facts.sql</x:v>
       </x:c>
-      <x:c r="V59" s="5" t="str">
+      <x:c r="W59" s="5" t="str">
         <x:v>id; fact_id; review_status; rationale; reviewed_by; reviewed_at</x:v>
       </x:c>
-      <x:c r="W59" s="5" t="str">
+      <x:c r="X59" s="5" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="X59" s="5" t="str">
+      <x:c r="Y59" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -4641,30 +4819,33 @@
       </x:c>
       <x:c r="O60" s="5" t="str"/>
       <x:c r="P60" s="5" t="str">
-        <x:v>knowledge.vendor</x:v>
+        <x:v>knowledge.proposal_fact_assertion</x:v>
       </x:c>
       <x:c r="Q60" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R60" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R60" s="5" t="str">
+      <x:c r="S60" s="5" t="str">
         <x:v>Contains enterprise-meaningful accepted, factual, commercial, metric, risk, or control data that should link through canonical IDs after review.</x:v>
       </x:c>
-      <x:c r="S60" s="5" t="str">
+      <x:c r="T60" s="5" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="T60" s="5" t="str">
+      <x:c r="U60" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U60" s="5" t="str">
+      <x:c r="V60" s="5" t="str">
         <x:v>supabase/migrations/20260725190000_source_vendor_proposal_facts.sql</x:v>
       </x:c>
-      <x:c r="V60" s="5" t="str">
+      <x:c r="W60" s="5" t="str">
         <x:v>id; client_key; source_event_id; vendor_key; proposal_artifact_id; fact_key; section_key; page_or_location; value_numeric; value_text; unit; currency; effective_period_start; effective_period_end; source_quote; source_pointer; confidence; extraction_method; supersedes_fact_id; created_by; created_at</x:v>
       </x:c>
-      <x:c r="W60" s="5" t="str">
+      <x:c r="X60" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X60" s="5" t="str">
+      <x:c r="Y60" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -4713,30 +4894,33 @@
       </x:c>
       <x:c r="O61" s="5" t="str"/>
       <x:c r="P61" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q61" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R61" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R61" s="5" t="str">
+      <x:c r="S61" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S61" s="5" t="str">
+      <x:c r="T61" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T61" s="5" t="str">
+      <x:c r="U61" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U61" s="5" t="str">
+      <x:c r="V61" s="5" t="str">
         <x:v>supabase/migrations/20260421152501_intelligence_layer_core.sql</x:v>
       </x:c>
-      <x:c r="V61" s="5" t="str">
+      <x:c r="W61" s="5" t="str">
         <x:v>id; client_id; name; description; modality; connector_type; source_location; credentials_reference; refresh_schedule; kpi_ids_populated; scope_description; data_format; residency_mode; retention_policy; compliance_tags; regulatory_notes; reasoning_scope_id; disclosure_scope_id; onboarded_at; onboarded_by_person_id; program_association; sunset_policy; access_log_reference; last_accessed_at</x:v>
       </x:c>
-      <x:c r="W61" s="5" t="str">
+      <x:c r="X61" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X61" s="5" t="str">
+      <x:c r="Y61" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -4785,30 +4969,33 @@
       </x:c>
       <x:c r="O62" s="5" t="str"/>
       <x:c r="P62" s="5" t="str">
-        <x:v>knowledge.vendor</x:v>
+        <x:v>knowledge.contract</x:v>
       </x:c>
       <x:c r="Q62" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R62" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R62" s="5" t="str">
+      <x:c r="S62" s="5" t="str">
         <x:v>Contains enterprise-meaningful accepted, factual, commercial, metric, risk, or control data that should link through canonical IDs after review.</x:v>
       </x:c>
-      <x:c r="S62" s="5" t="str">
+      <x:c r="T62" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="T62" s="5" t="str">
+      <x:c r="U62" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U62" s="5" t="str">
+      <x:c r="V62" s="5" t="str">
         <x:v>supabase/migrations/20260523090000_client_extension_it_productivity.sql</x:v>
       </x:c>
-      <x:c r="V62" s="5" t="str">
+      <x:c r="W62" s="5" t="str">
         <x:v>id; client_id; vendor_id; vendor_name; contract_name; contract_category; scope_summary; owner_id; annual_contract_value_usd; start_date; end_date; renewal_date; ai_usage_clauses; indemnity_provided; exit_terms_jsonb; concentration_pct; rate_card_vintage; outcome_based; created_at; updated_at; created_by; updated_by; deleted_at</x:v>
       </x:c>
-      <x:c r="W62" s="5" t="str">
+      <x:c r="X62" s="5" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="X62" s="5" t="str">
+      <x:c r="Y62" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -4857,30 +5044,33 @@
       </x:c>
       <x:c r="O63" s="5" t="str"/>
       <x:c r="P63" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q63" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R63" s="5" t="str">
         <x:v>archive</x:v>
       </x:c>
-      <x:c r="R63" s="5" t="str">
+      <x:c r="S63" s="5" t="str">
         <x:v>Audit/history object should be retained but not promoted as enterprise truth.</x:v>
       </x:c>
-      <x:c r="S63" s="5" t="str">
+      <x:c r="T63" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T63" s="5" t="str">
+      <x:c r="U63" s="5" t="str">
         <x:v>Archive-only; no runtime cutover.</x:v>
       </x:c>
-      <x:c r="U63" s="5" t="str">
+      <x:c r="V63" s="5" t="str">
         <x:v>supabase/migrations/20260628202000_cio_tower_schema_v1.sql</x:v>
       </x:c>
-      <x:c r="V63" s="5" t="str">
+      <x:c r="W63" s="5" t="str">
         <x:v>trace_key; tenant_key; surface; user_question; contract_key; measure_key; prompt_package_key; raw_model_response; rendered_response; artifacts; validation_status; validation_errors; latency_ms; model_name; created_at</x:v>
       </x:c>
-      <x:c r="W63" s="5" t="str">
+      <x:c r="X63" s="5" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="X63" s="5" t="str">
+      <x:c r="Y63" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -4929,30 +5119,33 @@
       </x:c>
       <x:c r="O64" s="5" t="str"/>
       <x:c r="P64" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q64" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R64" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R64" s="5" t="str">
+      <x:c r="S64" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S64" s="5" t="str">
+      <x:c r="T64" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T64" s="5" t="str">
+      <x:c r="U64" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U64" s="5" t="str">
+      <x:c r="V64" s="5" t="str">
         <x:v>supabase/migrations/20260628202000_cio_tower_schema_v1.sql</x:v>
       </x:c>
-      <x:c r="V64" s="5" t="str">
+      <x:c r="W64" s="5" t="str">
         <x:v>entity_key; tenant_key; entity_type; display_name; parent_entity_key; source_key; source_row; attributes; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W64" s="5" t="str">
+      <x:c r="X64" s="5" t="str">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="X64" s="5" t="str">
+      <x:c r="Y64" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -5004,27 +5197,30 @@
         <x:v>knowledge.metric_observation</x:v>
       </x:c>
       <x:c r="Q65" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R65" s="5" t="str">
         <x:v>project_shared_consumption</x:v>
       </x:c>
-      <x:c r="R65" s="5" t="str">
+      <x:c r="S65" s="5" t="str">
         <x:v>Tower facts are measure observations/read-model inputs; definitions and source facts must be governed separately.</x:v>
       </x:c>
-      <x:c r="S65" s="5" t="str">
+      <x:c r="T65" s="5" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="T65" s="5" t="str">
+      <x:c r="U65" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="U65" s="5" t="str">
+      <x:c r="V65" s="5" t="str">
         <x:v>supabase/migrations/20260628202000_cio_tower_schema_v1.sql</x:v>
       </x:c>
-      <x:c r="V65" s="5" t="str">
+      <x:c r="W65" s="5" t="str">
         <x:v>fact_key; tenant_key; entity_key; entity_type; measure; scope; view; amount_type; basis; period; value_numeric; value_text; value_date; value_bool; unit; value_source; confidence; source_key; source_row; formula_key; formula_version; is_rollup_of; component_of; superseded_by</x:v>
       </x:c>
-      <x:c r="W65" s="5" t="str">
+      <x:c r="X65" s="5" t="str">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="X65" s="5" t="str">
+      <x:c r="Y65" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -5073,30 +5269,33 @@
       </x:c>
       <x:c r="O66" s="5" t="str"/>
       <x:c r="P66" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q66" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R66" s="5" t="str">
         <x:v>project_shared_consumption</x:v>
       </x:c>
-      <x:c r="R66" s="5" t="str">
+      <x:c r="S66" s="5" t="str">
         <x:v>Derived object shaped for reuse by screens, reports, exports, or aVa.</x:v>
       </x:c>
-      <x:c r="S66" s="5" t="str">
+      <x:c r="T66" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="T66" s="5" t="str">
+      <x:c r="U66" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="U66" s="5" t="str">
+      <x:c r="V66" s="5" t="str">
         <x:v>supabase/migrations/20260717164000_cio_tower_command_mart_v1.sql</x:v>
       </x:c>
-      <x:c r="V66" s="5" t="str">
+      <x:c r="W66" s="5" t="str">
         <x:v>ai_portfolio_key; tenant_key; item_name; item_kind; vendor_name; system_name; ai_spend_type; ai_spend_category; funding_status; decision_lane; approved_funding_usd; ai_tagged_spend_usd; promised_value_usd; finance_validated_value_usd; usage_metric; usage_actual; adoption_rate_pct; value_score; readiness_score; risk_score; platform_embedded_ai_flag; duplicate_risk; value_claim_status; tower_claim_allowed</x:v>
       </x:c>
-      <x:c r="W66" s="5" t="str">
+      <x:c r="X66" s="5" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="X66" s="5" t="str">
+      <x:c r="Y66" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -5145,30 +5344,33 @@
       </x:c>
       <x:c r="O67" s="5" t="str"/>
       <x:c r="P67" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q67" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R67" s="5" t="str">
         <x:v>project_shared_consumption</x:v>
       </x:c>
-      <x:c r="R67" s="5" t="str">
+      <x:c r="S67" s="5" t="str">
         <x:v>Derived object shaped for reuse by screens, reports, exports, or aVa.</x:v>
       </x:c>
-      <x:c r="S67" s="5" t="str">
+      <x:c r="T67" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="T67" s="5" t="str">
+      <x:c r="U67" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="U67" s="5" t="str">
+      <x:c r="V67" s="5" t="str">
         <x:v>supabase/migrations/20260717164000_cio_tower_command_mart_v1.sql</x:v>
       </x:c>
-      <x:c r="V67" s="5" t="str">
+      <x:c r="W67" s="5" t="str">
         <x:v>command_center_key; tenant_key; tenant_name; mart_version; source_standard; formula_version; source_run_id; total_it_budget_fy26; run_budget_fy26; change_budget_fy26; approved_program_budget_fy26; ai_tagged_spend_fy26_non_additive; promised_value_fy26; partial_finance_validated_value_ytd; realized_value_ytd_allowed; candidate_ai_opportunities; watch_pressure_signals; run_ratio; change_ratio; finance_validation_ratio; decision_question; executive_summary; source_fact_keys; source_files</x:v>
       </x:c>
-      <x:c r="W67" s="5" t="str">
+      <x:c r="X67" s="5" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="X67" s="5" t="str">
+      <x:c r="Y67" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -5217,30 +5419,33 @@
       </x:c>
       <x:c r="O68" s="5" t="str"/>
       <x:c r="P68" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q68" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R68" s="5" t="str">
         <x:v>project_shared_consumption</x:v>
       </x:c>
-      <x:c r="R68" s="5" t="str">
+      <x:c r="S68" s="5" t="str">
         <x:v>Derived object shaped for reuse by screens, reports, exports, or aVa.</x:v>
       </x:c>
-      <x:c r="S68" s="5" t="str">
+      <x:c r="T68" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="T68" s="5" t="str">
+      <x:c r="U68" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="U68" s="5" t="str">
+      <x:c r="V68" s="5" t="str">
         <x:v>supabase/migrations/20260717164000_cio_tower_command_mart_v1.sql</x:v>
       </x:c>
-      <x:c r="V68" s="5" t="str">
+      <x:c r="W68" s="5" t="str">
         <x:v>action_key; tenant_key; sequence; action_lane; title; action_body; owner_hint; module_handoff; evidence_ids; source_fact_keys; formula_version; updated_at</x:v>
       </x:c>
-      <x:c r="W68" s="5" t="str">
+      <x:c r="X68" s="5" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="X68" s="5" t="str">
+      <x:c r="Y68" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -5292,27 +5497,30 @@
         <x:v>knowledge.evidence</x:v>
       </x:c>
       <x:c r="Q69" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R69" s="5" t="str">
         <x:v>project_shared_consumption</x:v>
       </x:c>
-      <x:c r="R69" s="5" t="str">
+      <x:c r="S69" s="5" t="str">
         <x:v>Derived object shaped for reuse by screens, reports, exports, or aVa.</x:v>
       </x:c>
-      <x:c r="S69" s="5" t="str">
+      <x:c r="T69" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="T69" s="5" t="str">
+      <x:c r="U69" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="U69" s="5" t="str">
+      <x:c r="V69" s="5" t="str">
         <x:v>supabase/migrations/20260717164000_cio_tower_command_mart_v1.sql</x:v>
       </x:c>
-      <x:c r="V69" s="5" t="str">
+      <x:c r="W69" s="5" t="str">
         <x:v>lineage_key; tenant_key; surface_section; displayed_fact; displayed_value_text; displayed_value_numeric; source_file; source_row; source_system; source_fact_keys; formula_version; caveat; updated_at</x:v>
       </x:c>
-      <x:c r="W69" s="5" t="str">
+      <x:c r="X69" s="5" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="X69" s="5" t="str">
+      <x:c r="Y69" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -5364,27 +5572,30 @@
         <x:v>knowledge.program</x:v>
       </x:c>
       <x:c r="Q70" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R70" s="5" t="str">
         <x:v>project_shared_consumption</x:v>
       </x:c>
-      <x:c r="R70" s="5" t="str">
+      <x:c r="S70" s="5" t="str">
         <x:v>Derived object shaped for reuse by screens, reports, exports, or aVa.</x:v>
       </x:c>
-      <x:c r="S70" s="5" t="str">
+      <x:c r="T70" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="T70" s="5" t="str">
+      <x:c r="U70" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="U70" s="5" t="str">
+      <x:c r="V70" s="5" t="str">
         <x:v>supabase/migrations/20260717164000_cio_tower_command_mart_v1.sql</x:v>
       </x:c>
-      <x:c r="V70" s="5" t="str">
+      <x:c r="W70" s="5" t="str">
         <x:v>lane_key; tenant_key; program_code; program_name; owner_role; finance_owner_role; decision_lane; decision_rationale; approved_funding_usd; ai_tagged_spend_usd; promised_value_usd; finance_validated_value_usd; usage_metric; usage_actual; adoption_rate_pct; value_claim_status; tower_claim_allowed; required_gates; caveat; evidence_ids; source_fact_keys; source_file; source_row; formula_version</x:v>
       </x:c>
-      <x:c r="W70" s="5" t="str">
+      <x:c r="X70" s="5" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="X70" s="5" t="str">
+      <x:c r="Y70" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -5433,30 +5644,33 @@
       </x:c>
       <x:c r="O71" s="5" t="str"/>
       <x:c r="P71" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q71" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R71" s="5" t="str">
         <x:v>project_shared_consumption</x:v>
       </x:c>
-      <x:c r="R71" s="5" t="str">
+      <x:c r="S71" s="5" t="str">
         <x:v>Derived object shaped for reuse by screens, reports, exports, or aVa.</x:v>
       </x:c>
-      <x:c r="S71" s="5" t="str">
+      <x:c r="T71" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="T71" s="5" t="str">
+      <x:c r="U71" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="U71" s="5" t="str">
+      <x:c r="V71" s="5" t="str">
         <x:v>supabase/migrations/20260717164000_cio_tower_command_mart_v1.sql</x:v>
       </x:c>
-      <x:c r="V71" s="5" t="str">
+      <x:c r="W71" s="5" t="str">
         <x:v>gap_key; tenant_key; mart_table; mart_record_key; required_field; source_template; source_record_id; severity; owner_hint; remediation_action; blocking; formula_version; created_at</x:v>
       </x:c>
-      <x:c r="W71" s="5" t="str">
+      <x:c r="X71" s="5" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="X71" s="5" t="str">
+      <x:c r="Y71" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -5507,30 +5721,33 @@
         <x:v>Metric/value/cost family candidate</x:v>
       </x:c>
       <x:c r="P72" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q72" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R72" s="5" t="str">
         <x:v>project_shared_consumption</x:v>
       </x:c>
-      <x:c r="R72" s="5" t="str">
+      <x:c r="S72" s="5" t="str">
         <x:v>Derived object shaped for reuse by screens, reports, exports, or aVa.</x:v>
       </x:c>
-      <x:c r="S72" s="5" t="str">
+      <x:c r="T72" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="T72" s="5" t="str">
+      <x:c r="U72" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="U72" s="5" t="str">
+      <x:c r="V72" s="5" t="str">
         <x:v>supabase/migrations/20260717164000_cio_tower_command_mart_v1.sql</x:v>
       </x:c>
-      <x:c r="V72" s="5" t="str">
+      <x:c r="W72" s="5" t="str">
         <x:v>funnel_key; tenant_key; sequence; stage_key; stage_label; value_numeric; denominator_stage_key; conversion_ratio; claim_status; caveat; source_fact_keys; source_file; source_row; formula_version; updated_at</x:v>
       </x:c>
-      <x:c r="W72" s="5" t="str">
+      <x:c r="X72" s="5" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="X72" s="5" t="str">
+      <x:c r="Y72" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -5582,27 +5799,30 @@
         <x:v>knowledge.metric_observation</x:v>
       </x:c>
       <x:c r="Q73" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R73" s="5" t="str">
         <x:v>project_shared_consumption</x:v>
       </x:c>
-      <x:c r="R73" s="5" t="str">
+      <x:c r="S73" s="5" t="str">
         <x:v>Tower metric observations are calculated/published results for shared consumption after parity proof.</x:v>
       </x:c>
-      <x:c r="S73" s="5" t="str">
+      <x:c r="T73" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="T73" s="5" t="str">
+      <x:c r="U73" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="U73" s="5" t="str">
+      <x:c r="V73" s="5" t="str">
         <x:v>supabase/migrations/20260628202000_cio_tower_schema_v1.sql</x:v>
       </x:c>
-      <x:c r="V73" s="5" t="str">
+      <x:c r="W73" s="5" t="str">
         <x:v>result_key; tenant_key; measure_key; scope; period; basis; dimensions; value_numeric; value_json; source_fact_keys; formula_version; computed_at</x:v>
       </x:c>
-      <x:c r="W73" s="5" t="str">
+      <x:c r="X73" s="5" t="str">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="X73" s="5" t="str">
+      <x:c r="Y73" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -5654,27 +5874,30 @@
         <x:v>knowledge.metric_definition</x:v>
       </x:c>
       <x:c r="Q74" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R74" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R74" s="5" t="str">
+      <x:c r="S74" s="5" t="str">
         <x:v>Tower metric definitions should link to the shared metric definition registry.</x:v>
       </x:c>
-      <x:c r="S74" s="5" t="str">
+      <x:c r="T74" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="T74" s="5" t="str">
+      <x:c r="U74" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U74" s="5" t="str">
+      <x:c r="V74" s="5" t="str">
         <x:v>supabase/migrations/20260628202000_cio_tower_schema_v1.sql</x:v>
       </x:c>
-      <x:c r="V74" s="5" t="str">
+      <x:c r="W74" s="5" t="str">
         <x:v>measure_key; label; description; default_scope; grain_filter; group_by; aggregation; numerator_filter; denominator_filter; reconciles_to_measure_key; honesty_rule; artifact_default; formula; formula_version; active; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W74" s="5" t="str">
+      <x:c r="X74" s="5" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="X74" s="5" t="str">
+      <x:c r="Y74" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -5723,30 +5946,33 @@
       </x:c>
       <x:c r="O75" s="5" t="str"/>
       <x:c r="P75" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q75" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R75" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R75" s="5" t="str">
+      <x:c r="S75" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S75" s="5" t="str">
+      <x:c r="T75" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T75" s="5" t="str">
+      <x:c r="U75" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U75" s="5" t="str">
+      <x:c r="V75" s="5" t="str">
         <x:v>supabase/migrations/20260628202000_cio_tower_schema_v1.sql</x:v>
       </x:c>
-      <x:c r="V75" s="5" t="str">
+      <x:c r="W75" s="5" t="str">
         <x:v>prompt_package_key; tenant_key; surface; user_question; contract_key; measure_key; deterministic_packet; prompt_text; prompt_hash; model_name; created_at</x:v>
       </x:c>
-      <x:c r="W75" s="5" t="str">
+      <x:c r="X75" s="5" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="X75" s="5" t="str">
+      <x:c r="Y75" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -5798,27 +6024,30 @@
         <x:v>product.tower_question_contract</x:v>
       </x:c>
       <x:c r="Q76" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R76" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R76" s="5" t="str">
+      <x:c r="S76" s="5" t="str">
         <x:v>Question contracts govern Tower answer behavior; they are product configuration, not vendor contracts.</x:v>
       </x:c>
-      <x:c r="S76" s="5" t="str">
+      <x:c r="T76" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T76" s="5" t="str">
+      <x:c r="U76" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U76" s="5" t="str">
+      <x:c r="V76" s="5" t="str">
         <x:v>supabase/migrations/20260628202000_cio_tower_schema_v1.sql</x:v>
       </x:c>
-      <x:c r="V76" s="5" t="str">
+      <x:c r="W76" s="5" t="str">
         <x:v>contract_key; surface; intent; question_family; measure_key; default_scope; dimensions; filters_schema; required_fields; artifact_type; outside_scope_rule; prompt_policy_key; visible_answer_contract; examples; active; created_at</x:v>
       </x:c>
-      <x:c r="W76" s="5" t="str">
+      <x:c r="X76" s="5" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="X76" s="5" t="str">
+      <x:c r="Y76" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -5867,30 +6096,33 @@
       </x:c>
       <x:c r="O77" s="5" t="str"/>
       <x:c r="P77" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q77" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R77" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R77" s="5" t="str">
+      <x:c r="S77" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S77" s="5" t="str">
+      <x:c r="T77" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T77" s="5" t="str">
+      <x:c r="U77" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U77" s="5" t="str">
+      <x:c r="V77" s="5" t="str">
         <x:v>supabase/migrations/20260628202000_cio_tower_schema_v1.sql</x:v>
       </x:c>
-      <x:c r="V77" s="5" t="str">
+      <x:c r="W77" s="5" t="str">
         <x:v>relationship_key; tenant_key; from_entity_key; to_entity_key; relationship_type; confidence; source_key; source_row; attributes; created_at</x:v>
       </x:c>
-      <x:c r="W77" s="5" t="str">
+      <x:c r="X77" s="5" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="X77" s="5" t="str">
+      <x:c r="Y77" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -5939,30 +6171,33 @@
       </x:c>
       <x:c r="O78" s="5" t="str"/>
       <x:c r="P78" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q78" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R78" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R78" s="5" t="str">
+      <x:c r="S78" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S78" s="5" t="str">
+      <x:c r="T78" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T78" s="5" t="str">
+      <x:c r="U78" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U78" s="5" t="str">
+      <x:c r="V78" s="5" t="str">
         <x:v>supabase/migrations/20260628202000_cio_tower_schema_v1.sql</x:v>
       </x:c>
-      <x:c r="V78" s="5" t="str">
+      <x:c r="W78" s="5" t="str">
         <x:v>source_key; tenant_key; source_system; source_file; source_kind; source_version; upload_run_id; loaded_at; freshness_date; trust_tier; row_count; metadata</x:v>
       </x:c>
-      <x:c r="W78" s="5" t="str">
+      <x:c r="X78" s="5" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="X78" s="5" t="str">
+      <x:c r="Y78" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -6011,30 +6246,33 @@
       </x:c>
       <x:c r="O79" s="5" t="str"/>
       <x:c r="P79" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q79" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R79" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R79" s="5" t="str">
+      <x:c r="S79" s="5" t="str">
         <x:v>Contains enterprise-meaningful accepted, factual, commercial, metric, risk, or control data that should link through canonical IDs after review.</x:v>
       </x:c>
-      <x:c r="S79" s="5" t="str">
+      <x:c r="T79" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="T79" s="5" t="str">
+      <x:c r="U79" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U79" s="5" t="str">
+      <x:c r="V79" s="5" t="str">
         <x:v>supabase/migrations/20260721160000_cio_tower_tool_identity_aliases_v1.sql</x:v>
       </x:c>
-      <x:c r="V79" s="5" t="str">
+      <x:c r="W79" s="5" t="str">
         <x:v>alias_key; tenant_key; canonical_tool_key; alias; vendor_name; system_name; program_code; canonical_program_key; source; active; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W79" s="5" t="str">
+      <x:c r="X79" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X79" s="5" t="str">
+      <x:c r="Y79" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -6083,30 +6321,33 @@
       </x:c>
       <x:c r="O80" s="5" t="str"/>
       <x:c r="P80" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q80" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R80" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R80" s="5" t="str">
+      <x:c r="S80" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S80" s="5" t="str">
+      <x:c r="T80" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T80" s="5" t="str">
+      <x:c r="U80" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U80" s="5" t="str">
+      <x:c r="V80" s="5" t="str">
         <x:v>supabase/migrations/20260628202000_cio_tower_schema_v1.sql</x:v>
       </x:c>
-      <x:c r="V80" s="5" t="str">
+      <x:c r="W80" s="5" t="str">
         <x:v>validation_result_key; validation_run_key; tenant_key; question; expected; actual; status; notes; created_at</x:v>
       </x:c>
-      <x:c r="W80" s="5" t="str">
+      <x:c r="X80" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X80" s="5" t="str">
+      <x:c r="Y80" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -6155,30 +6396,33 @@
       </x:c>
       <x:c r="O81" s="5" t="str"/>
       <x:c r="P81" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q81" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R81" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R81" s="5" t="str">
+      <x:c r="S81" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S81" s="5" t="str">
+      <x:c r="T81" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T81" s="5" t="str">
+      <x:c r="U81" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U81" s="5" t="str">
+      <x:c r="V81" s="5" t="str">
         <x:v>supabase/migrations/20260628202000_cio_tower_schema_v1.sql</x:v>
       </x:c>
-      <x:c r="V81" s="5" t="str">
+      <x:c r="W81" s="5" t="str">
         <x:v>validation_run_key; run_type; tenant_key; started_at; finished_at; status; summary</x:v>
       </x:c>
-      <x:c r="W81" s="5" t="str">
+      <x:c r="X81" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X81" s="5" t="str">
+      <x:c r="Y81" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -6230,27 +6474,30 @@
         <x:v>governance.publication_contract_version</x:v>
       </x:c>
       <x:c r="Q82" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R82" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R82" s="5" t="str">
+      <x:c r="S82" s="5" t="str">
         <x:v>Active contract-version pointers are runtime governance/configuration, not commercial contract facts.</x:v>
       </x:c>
-      <x:c r="S82" s="5" t="str">
+      <x:c r="T82" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T82" s="5" t="str">
+      <x:c r="U82" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U82" s="5" t="str">
+      <x:c r="V82" s="5" t="str">
         <x:v>supabase/migrations/20260709203000_intelligence_v7_moat_foundation.sql</x:v>
       </x:c>
-      <x:c r="V82" s="5" t="str">
+      <x:c r="W82" s="5" t="str">
         <x:v>tenant_key; active_contract_version; candidate_contract_version; rollback_contract_version; promotion_status; promoted_by; promoted_at; proof_bundle_uri; promotion_notes; metadata; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W82" s="5" t="str">
+      <x:c r="X82" s="5" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="X82" s="5" t="str">
+      <x:c r="Y82" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -6299,30 +6546,33 @@
       </x:c>
       <x:c r="O83" s="5" t="str"/>
       <x:c r="P83" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
+        <x:v>knowledge.action_or_decision</x:v>
       </x:c>
       <x:c r="Q83" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R83" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R83" s="5" t="str">
+      <x:c r="S83" s="5" t="str">
         <x:v>Contains enterprise-meaningful accepted, factual, commercial, metric, risk, or control data that should link through canonical IDs after review.</x:v>
       </x:c>
-      <x:c r="S83" s="5" t="str">
+      <x:c r="T83" s="5" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="T83" s="5" t="str">
+      <x:c r="U83" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U83" s="5" t="str">
+      <x:c r="V83" s="5" t="str">
         <x:v>supabase/migrations/20260616170000_ai_control_tower_substrate.sql; supabase/migrations/20260722220000_ai_control_substrate_drift_repair.sql</x:v>
       </x:c>
-      <x:c r="V83" s="5" t="str">
+      <x:c r="W83" s="5" t="str">
         <x:v>id; client_id; refresh_run_id; action_key; related_record_type; related_record_key; posture; title; rationale; owner_role; due_date; status; evidence_state; payload; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W83" s="5" t="str">
+      <x:c r="X83" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X83" s="5" t="str">
+      <x:c r="Y83" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -6373,30 +6623,33 @@
         <x:v>Metric/value/cost family candidate</x:v>
       </x:c>
       <x:c r="P84" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
+        <x:v>knowledge.outcome</x:v>
       </x:c>
       <x:c r="Q84" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R84" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R84" s="5" t="str">
+      <x:c r="S84" s="5" t="str">
         <x:v>Contains enterprise-meaningful accepted, factual, commercial, metric, risk, or control data that should link through canonical IDs after review.</x:v>
       </x:c>
-      <x:c r="S84" s="5" t="str">
+      <x:c r="T84" s="5" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="T84" s="5" t="str">
+      <x:c r="U84" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U84" s="5" t="str">
+      <x:c r="V84" s="5" t="str">
         <x:v>supabase/migrations/20260616170000_ai_control_tower_substrate.sql; supabase/migrations/20260722220000_ai_control_substrate_drift_repair.sql</x:v>
       </x:c>
-      <x:c r="V84" s="5" t="str">
+      <x:c r="W84" s="5" t="str">
         <x:v>id; client_id; refresh_run_id; source_id; agent_key; vendor; module; agent_name; persona; workflow; eligible_volume; ai_touched_volume; auto_resolved_volume; cycle_time_before; cycle_time_after; quality_before; quality_after; monthly_spend_usd; evidence_state; payload; created_at</x:v>
       </x:c>
-      <x:c r="W84" s="5" t="str">
+      <x:c r="X84" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X84" s="5" t="str">
+      <x:c r="Y84" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -6448,27 +6701,30 @@
         <x:v>consumption.context_pack</x:v>
       </x:c>
       <x:c r="Q85" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R85" s="5" t="str">
         <x:v>project_shared_consumption</x:v>
       </x:c>
-      <x:c r="R85" s="5" t="str">
+      <x:c r="S85" s="5" t="str">
         <x:v>Context packs are derived read bundles for aVa/Tower consumption, not canonical source truth.</x:v>
       </x:c>
-      <x:c r="S85" s="5" t="str">
+      <x:c r="T85" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="T85" s="5" t="str">
+      <x:c r="U85" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="U85" s="5" t="str">
+      <x:c r="V85" s="5" t="str">
         <x:v>supabase/migrations/20260616170000_ai_control_tower_substrate.sql; supabase/migrations/20260722220000_ai_control_substrate_drift_repair.sql</x:v>
       </x:c>
-      <x:c r="V85" s="5" t="str">
+      <x:c r="W85" s="5" t="str">
         <x:v>id; client_id; refresh_run_id; pack_key; lens; question_intent; visible_metric_keys; context_json; evidence_keys; retrieval_verified; created_at</x:v>
       </x:c>
-      <x:c r="W85" s="5" t="str">
+      <x:c r="X85" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X85" s="5" t="str">
+      <x:c r="Y85" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -6517,30 +6773,33 @@
       </x:c>
       <x:c r="O86" s="5" t="str"/>
       <x:c r="P86" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
+        <x:v>knowledge.metric_observation</x:v>
       </x:c>
       <x:c r="Q86" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R86" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R86" s="5" t="str">
+      <x:c r="S86" s="5" t="str">
         <x:v>Contains enterprise-meaningful accepted, factual, commercial, metric, risk, or control data that should link through canonical IDs after review.</x:v>
       </x:c>
-      <x:c r="S86" s="5" t="str">
+      <x:c r="T86" s="5" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="T86" s="5" t="str">
+      <x:c r="U86" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U86" s="5" t="str">
+      <x:c r="V86" s="5" t="str">
         <x:v>supabase/migrations/20260616170000_ai_control_tower_substrate.sql; supabase/migrations/20260722220000_ai_control_substrate_drift_repair.sql</x:v>
       </x:c>
-      <x:c r="V86" s="5" t="str">
+      <x:c r="W86" s="5" t="str">
         <x:v>id; client_id; refresh_run_id; source_id; benefit_key; initiative_key; benefit_name; metric_key; baseline_value; current_value; target_value; promised_annual_value_usd; realized_annual_value_usd; confidence; readiness_state; evidence_state; payload; created_at</x:v>
       </x:c>
-      <x:c r="W86" s="5" t="str">
+      <x:c r="X86" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X86" s="5" t="str">
+      <x:c r="Y86" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -6589,30 +6848,33 @@
       </x:c>
       <x:c r="O87" s="5" t="str"/>
       <x:c r="P87" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
+        <x:v>knowledge.fact_assertion</x:v>
       </x:c>
       <x:c r="Q87" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R87" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R87" s="5" t="str">
+      <x:c r="S87" s="5" t="str">
         <x:v>Contains enterprise-meaningful accepted, factual, commercial, metric, risk, or control data that should link through canonical IDs after review.</x:v>
       </x:c>
-      <x:c r="S87" s="5" t="str">
+      <x:c r="T87" s="5" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="T87" s="5" t="str">
+      <x:c r="U87" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U87" s="5" t="str">
+      <x:c r="V87" s="5" t="str">
         <x:v>supabase/migrations/20260616170000_ai_control_tower_substrate.sql; supabase/migrations/20260722220000_ai_control_substrate_drift_repair.sql</x:v>
       </x:c>
-      <x:c r="V87" s="5" t="str">
+      <x:c r="W87" s="5" t="str">
         <x:v>id; client_id; refresh_run_id; record_type; record_key; fact_key; fact_type; fact_value; fact_text; period_start; period_end; confidence; evidence_state; evidence_keys; payload; created_at</x:v>
       </x:c>
-      <x:c r="W87" s="5" t="str">
+      <x:c r="X87" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X87" s="5" t="str">
+      <x:c r="Y87" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -6661,30 +6923,33 @@
       </x:c>
       <x:c r="O88" s="5" t="str"/>
       <x:c r="P88" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
+        <x:v>knowledge.relationship_assertion</x:v>
       </x:c>
       <x:c r="Q88" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R88" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R88" s="5" t="str">
+      <x:c r="S88" s="5" t="str">
         <x:v>Contains enterprise-meaningful accepted, factual, commercial, metric, risk, or control data that should link through canonical IDs after review.</x:v>
       </x:c>
-      <x:c r="S88" s="5" t="str">
+      <x:c r="T88" s="5" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="T88" s="5" t="str">
+      <x:c r="U88" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U88" s="5" t="str">
+      <x:c r="V88" s="5" t="str">
         <x:v>supabase/migrations/20260616170000_ai_control_tower_substrate.sql; supabase/migrations/20260722220000_ai_control_substrate_drift_repair.sql</x:v>
       </x:c>
-      <x:c r="V88" s="5" t="str">
+      <x:c r="W88" s="5" t="str">
         <x:v>id; client_id; refresh_run_id; relationship_key; relationship_type; from_record_type; from_record_key; to_record_type; to_record_key; properties; created_at</x:v>
       </x:c>
-      <x:c r="W88" s="5" t="str">
+      <x:c r="X88" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X88" s="5" t="str">
+      <x:c r="Y88" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -6735,30 +7000,33 @@
         <x:v>Metric/value/cost family candidate</x:v>
       </x:c>
       <x:c r="P89" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
+        <x:v>knowledge.metric_observation</x:v>
       </x:c>
       <x:c r="Q89" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R89" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R89" s="5" t="str">
+      <x:c r="S89" s="5" t="str">
         <x:v>Contains enterprise-meaningful accepted, factual, commercial, metric, risk, or control data that should link through canonical IDs after review.</x:v>
       </x:c>
-      <x:c r="S89" s="5" t="str">
+      <x:c r="T89" s="5" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="T89" s="5" t="str">
+      <x:c r="U89" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U89" s="5" t="str">
+      <x:c r="V89" s="5" t="str">
         <x:v>supabase/migrations/20260616170000_ai_control_tower_substrate.sql; supabase/migrations/20260722220000_ai_control_substrate_drift_repair.sql</x:v>
       </x:c>
-      <x:c r="V89" s="5" t="str">
+      <x:c r="W89" s="5" t="str">
         <x:v>id; client_id; refresh_run_id; source_id; team; repo; tool_key; period_start; period_end; deployment_frequency_before; deployment_frequency_after; lead_time_hours_before; lead_time_hours_after; change_failure_rate_pct_before; change_failure_rate_pct_after; mttr_hours_before; mttr_hours_after; sample_size_deploys; evidence_state; payload; created_at</x:v>
       </x:c>
-      <x:c r="W89" s="5" t="str">
+      <x:c r="X89" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X89" s="5" t="str">
+      <x:c r="Y89" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -6807,30 +7075,33 @@
       </x:c>
       <x:c r="O90" s="5" t="str"/>
       <x:c r="P90" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
+        <x:v>knowledge.evidence</x:v>
       </x:c>
       <x:c r="Q90" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R90" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R90" s="5" t="str">
+      <x:c r="S90" s="5" t="str">
         <x:v>Contains enterprise-meaningful accepted, factual, commercial, metric, risk, or control data that should link through canonical IDs after review.</x:v>
       </x:c>
-      <x:c r="S90" s="5" t="str">
+      <x:c r="T90" s="5" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="T90" s="5" t="str">
+      <x:c r="U90" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U90" s="5" t="str">
+      <x:c r="V90" s="5" t="str">
         <x:v>supabase/migrations/20260616170000_ai_control_tower_substrate.sql; supabase/migrations/20260722220000_ai_control_substrate_drift_repair.sql</x:v>
       </x:c>
-      <x:c r="V90" s="5" t="str">
+      <x:c r="W90" s="5" t="str">
         <x:v>id; client_id; refresh_run_id; evidence_key; record_type; record_key; evidence_type; citation_label; citation_locator; evidence_pointer; evidence_state; confidence; payload; created_at</x:v>
       </x:c>
-      <x:c r="W90" s="5" t="str">
+      <x:c r="X90" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X90" s="5" t="str">
+      <x:c r="Y90" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -6882,27 +7153,30 @@
         <x:v>knowledge.program</x:v>
       </x:c>
       <x:c r="Q91" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R91" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R91" s="5" t="str">
+      <x:c r="S91" s="5" t="str">
         <x:v>Contains enterprise-meaningful accepted, factual, commercial, metric, risk, or control data that should link through canonical IDs after review.</x:v>
       </x:c>
-      <x:c r="S91" s="5" t="str">
+      <x:c r="T91" s="5" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="T91" s="5" t="str">
+      <x:c r="U91" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U91" s="5" t="str">
+      <x:c r="V91" s="5" t="str">
         <x:v>supabase/migrations/20260616170000_ai_control_tower_substrate.sql; supabase/migrations/20260722220000_ai_control_substrate_drift_repair.sql</x:v>
       </x:c>
-      <x:c r="V91" s="5" t="str">
+      <x:c r="W91" s="5" t="str">
         <x:v>id; client_id; refresh_run_id; source_id; initiative_key; initiative_name; category; stage; business_owner_role; executive_sponsor_role; vendor; tool_or_system; impacted_personas; promised_benefit; target_metric_key; baseline_value; target_value; target_date; status_flag; record_version; is_current; payload; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W91" s="5" t="str">
+      <x:c r="X91" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X91" s="5" t="str">
+      <x:c r="Y91" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -6951,30 +7225,33 @@
       </x:c>
       <x:c r="O92" s="5" t="str"/>
       <x:c r="P92" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
+        <x:v>knowledge.metric_observation</x:v>
       </x:c>
       <x:c r="Q92" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R92" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R92" s="5" t="str">
+      <x:c r="S92" s="5" t="str">
         <x:v>Contains enterprise-meaningful accepted, factual, commercial, metric, risk, or control data that should link through canonical IDs after review.</x:v>
       </x:c>
-      <x:c r="S92" s="5" t="str">
+      <x:c r="T92" s="5" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="T92" s="5" t="str">
+      <x:c r="U92" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U92" s="5" t="str">
+      <x:c r="V92" s="5" t="str">
         <x:v>supabase/migrations/20260616170000_ai_control_tower_substrate.sql; supabase/migrations/20260722220000_ai_control_substrate_drift_repair.sql</x:v>
       </x:c>
-      <x:c r="V92" s="5" t="str">
+      <x:c r="W92" s="5" t="str">
         <x:v>id; client_id; refresh_run_id; source_id; persona_key; persona_name; function_name; workflow; metric_key; unit; baseline_value; current_value; target_value; initiative_key; confidence; evidence_state; payload; created_at</x:v>
       </x:c>
-      <x:c r="W92" s="5" t="str">
+      <x:c r="X92" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X92" s="5" t="str">
+      <x:c r="Y92" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -7026,27 +7303,30 @@
         <x:v>operations.refresh_run</x:v>
       </x:c>
       <x:c r="Q93" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R93" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R93" s="5" t="str">
+      <x:c r="S93" s="5" t="str">
         <x:v>Refresh runs are operational lineage for Tower publication, not enterprise facts.</x:v>
       </x:c>
-      <x:c r="S93" s="5" t="str">
+      <x:c r="T93" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T93" s="5" t="str">
+      <x:c r="U93" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U93" s="5" t="str">
+      <x:c r="V93" s="5" t="str">
         <x:v>supabase/migrations/20260616170000_ai_control_tower_substrate.sql; supabase/migrations/20260722220000_ai_control_substrate_drift_repair.sql</x:v>
       </x:c>
-      <x:c r="V93" s="5" t="str">
+      <x:c r="W93" s="5" t="str">
         <x:v>id; client_id; client_key; refresh_run_key; reporting_period_start; reporting_period_end; run_type; status; source_count; rows_seen; rows_valid; rows_rejected; review_required_count; receipt_uri; parser_version; source_fingerprint; metadata; created_at; updated_at; committed_at; indexed_at; retrieval_verified_at</x:v>
       </x:c>
-      <x:c r="W93" s="5" t="str">
+      <x:c r="X93" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X93" s="5" t="str">
+      <x:c r="Y93" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -7098,27 +7378,30 @@
         <x:v>knowledge.risk_control</x:v>
       </x:c>
       <x:c r="Q94" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R94" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R94" s="5" t="str">
+      <x:c r="S94" s="5" t="str">
         <x:v>Contains enterprise-meaningful accepted, factual, commercial, metric, risk, or control data that should link through canonical IDs after review.</x:v>
       </x:c>
-      <x:c r="S94" s="5" t="str">
+      <x:c r="T94" s="5" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="T94" s="5" t="str">
+      <x:c r="U94" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U94" s="5" t="str">
+      <x:c r="V94" s="5" t="str">
         <x:v>supabase/migrations/20260616170000_ai_control_tower_substrate.sql; supabase/migrations/20260722220000_ai_control_substrate_drift_repair.sql</x:v>
       </x:c>
-      <x:c r="V94" s="5" t="str">
+      <x:c r="W94" s="5" t="str">
         <x:v>id; client_id; refresh_run_id; source_id; risk_key; initiative_key; dimension; severity; status; risk_description; owner_role; required_action; governance_gate; evidence_state; payload; created_at</x:v>
       </x:c>
-      <x:c r="W94" s="5" t="str">
+      <x:c r="X94" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X94" s="5" t="str">
+      <x:c r="Y94" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -7172,27 +7455,30 @@
         <x:v>knowledge.contract</x:v>
       </x:c>
       <x:c r="Q95" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R95" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R95" s="5" t="str">
+      <x:c r="S95" s="5" t="str">
         <x:v>Contains enterprise-meaningful accepted, factual, commercial, metric, risk, or control data that should link through canonical IDs after review.</x:v>
       </x:c>
-      <x:c r="S95" s="5" t="str">
+      <x:c r="T95" s="5" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="T95" s="5" t="str">
+      <x:c r="U95" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U95" s="5" t="str">
+      <x:c r="V95" s="5" t="str">
         <x:v>supabase/migrations/20260616170000_ai_control_tower_substrate.sql; supabase/migrations/20260722220000_ai_control_substrate_drift_repair.sql</x:v>
       </x:c>
-      <x:c r="V95" s="5" t="str">
+      <x:c r="W95" s="5" t="str">
         <x:v>id; client_id; refresh_run_id; source_id; spend_key; initiative_key; vendor; product_or_service; spend_type; monthly_spend_usd; annualized_spend_usd; renewal_date; unit_economics_metric; unit_economics_value; evidence_state; payload; created_at</x:v>
       </x:c>
-      <x:c r="W95" s="5" t="str">
+      <x:c r="X95" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X95" s="5" t="str">
+      <x:c r="Y95" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -7241,30 +7527,33 @@
       </x:c>
       <x:c r="O96" s="5" t="str"/>
       <x:c r="P96" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
+        <x:v>knowledge.metric_observation</x:v>
       </x:c>
       <x:c r="Q96" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R96" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R96" s="5" t="str">
+      <x:c r="S96" s="5" t="str">
         <x:v>Contains enterprise-meaningful accepted, factual, commercial, metric, risk, or control data that should link through canonical IDs after review.</x:v>
       </x:c>
-      <x:c r="S96" s="5" t="str">
+      <x:c r="T96" s="5" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="T96" s="5" t="str">
+      <x:c r="U96" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U96" s="5" t="str">
+      <x:c r="V96" s="5" t="str">
         <x:v>supabase/migrations/20260616170000_ai_control_tower_substrate.sql; supabase/migrations/20260722220000_ai_control_substrate_drift_repair.sql</x:v>
       </x:c>
-      <x:c r="V96" s="5" t="str">
+      <x:c r="W96" s="5" t="str">
         <x:v>id; client_id; refresh_run_id; source_id; tool_key; tool_name; vendor; user_group_or_team; persona; period_start; period_end; licensed_seats; active_users; usage_events; accepted_or_completed_events; utilization_pct; monthly_spend_usd; evidence_state; payload; created_at</x:v>
       </x:c>
-      <x:c r="W96" s="5" t="str">
+      <x:c r="X96" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X96" s="5" t="str">
+      <x:c r="Y96" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -7316,25 +7605,28 @@
         <x:v>knowledge.risk_control</x:v>
       </x:c>
       <x:c r="Q97" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R97" s="5" t="str">
         <x:v>project_shared_consumption</x:v>
       </x:c>
-      <x:c r="R97" s="5" t="str">
+      <x:c r="S97" s="5" t="str">
         <x:v>Derived object shaped for reuse by screens, reports, exports, or aVa.</x:v>
       </x:c>
-      <x:c r="S97" s="5" t="str">
+      <x:c r="T97" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="T97" s="5" t="str">
+      <x:c r="U97" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="U97" s="5" t="str">
+      <x:c r="V97" s="5" t="str">
         <x:v>supabase/migrations/20260621120000_ai_control_tower_lens_mv.sql</x:v>
       </x:c>
-      <x:c r="V97" s="5" t="str"/>
-      <x:c r="W97" s="5" t="str">
+      <x:c r="W97" s="5" t="str"/>
+      <x:c r="X97" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X97" s="5" t="str">
+      <x:c r="Y97" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -7383,30 +7675,33 @@
       </x:c>
       <x:c r="O98" s="5" t="str"/>
       <x:c r="P98" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q98" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R98" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R98" s="5" t="str">
+      <x:c r="S98" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S98" s="5" t="str">
+      <x:c r="T98" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T98" s="5" t="str">
+      <x:c r="U98" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U98" s="5" t="str">
+      <x:c r="V98" s="5" t="str">
         <x:v>supabase/migrations/20260523090000_client_extension_it_productivity.sql</x:v>
       </x:c>
-      <x:c r="V98" s="5" t="str">
+      <x:c r="W98" s="5" t="str">
         <x:v>id; client_id; tool_name; vendor; licensed_seats; activated_seats; dau; mau; annual_cost_usd; contract_end_date; indemnity_status; retention_policy; created_at; updated_at; created_by; updated_by; deleted_at</x:v>
       </x:c>
-      <x:c r="W98" s="5" t="str">
+      <x:c r="X98" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X98" s="5" t="str">
+      <x:c r="Y98" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -7458,27 +7753,30 @@
         <x:v>knowledge.application</x:v>
       </x:c>
       <x:c r="Q99" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R99" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R99" s="5" t="str">
+      <x:c r="S99" s="5" t="str">
         <x:v>Application/system inventory is an enterprise object family that should map to canonical application identity.</x:v>
       </x:c>
-      <x:c r="S99" s="5" t="str">
+      <x:c r="T99" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="T99" s="5" t="str">
+      <x:c r="U99" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U99" s="5" t="str">
+      <x:c r="V99" s="5" t="str">
         <x:v>supabase/migrations/20260523090000_client_extension_it_productivity.sql</x:v>
       </x:c>
-      <x:c r="V99" s="5" t="str">
+      <x:c r="W99" s="5" t="str">
         <x:v>id; client_id; app_id; name; stack; language; is_modern; change_rate_per_yr; fte_count; criticality_tier; time_classification; annual_run_cost_usd; ams_vendor_id; ams_contract_value_usd; sunset_decision_date; ai_fit_score; created_at; updated_at; created_by; updated_by; deleted_at; REFERENCES; ON</x:v>
       </x:c>
-      <x:c r="W99" s="5" t="str">
+      <x:c r="X99" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X99" s="5" t="str">
+      <x:c r="Y99" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -7530,27 +7828,30 @@
         <x:v>governance.tenant</x:v>
       </x:c>
       <x:c r="Q100" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R100" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R100" s="5" t="str">
+      <x:c r="S100" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S100" s="5" t="str">
+      <x:c r="T100" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T100" s="5" t="str">
+      <x:c r="U100" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U100" s="5" t="str">
+      <x:c r="V100" s="5" t="str">
         <x:v>supabase/migrations/020_clients_and_invoices.sql</x:v>
       </x:c>
-      <x:c r="V100" s="5" t="str">
+      <x:c r="W100" s="5" t="str">
         <x:v>id; name; legal_name; billing_email; stripe_customer_id; industry_code; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W100" s="5" t="str">
+      <x:c r="X100" s="5" t="str">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="X100" s="5" t="str">
+      <x:c r="Y100" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -7599,30 +7900,33 @@
       </x:c>
       <x:c r="O101" s="5" t="str"/>
       <x:c r="P101" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q101" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R101" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R101" s="5" t="str">
+      <x:c r="S101" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S101" s="5" t="str">
+      <x:c r="T101" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T101" s="5" t="str">
+      <x:c r="U101" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U101" s="5" t="str">
+      <x:c r="V101" s="5" t="str">
         <x:v>supabase/migrations/20260523090000_client_extension_it_productivity.sql</x:v>
       </x:c>
-      <x:c r="V101" s="5" t="str">
+      <x:c r="W101" s="5" t="str">
         <x:v>id; client_id; move_id; instrument_template_id; status; owner_id; due_date; completion_pct; evidence_link; t_tier; created_at; updated_at; created_by; updated_by; deleted_at</x:v>
       </x:c>
-      <x:c r="W101" s="5" t="str">
+      <x:c r="X101" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X101" s="5" t="str">
+      <x:c r="Y101" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -7673,30 +7977,33 @@
         <x:v>Metric/value/cost family candidate</x:v>
       </x:c>
       <x:c r="P102" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q102" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R102" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R102" s="5" t="str">
+      <x:c r="S102" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S102" s="5" t="str">
+      <x:c r="T102" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T102" s="5" t="str">
+      <x:c r="U102" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U102" s="5" t="str">
+      <x:c r="V102" s="5" t="str">
         <x:v>supabase/migrations/20260523090000_client_extension_it_productivity.sql</x:v>
       </x:c>
-      <x:c r="V102" s="5" t="str">
+      <x:c r="W102" s="5" t="str">
         <x:v>id; client_id; team_id; app_id; measured_at; deploy_freq_per_week; lead_time_hours; mttr_hours; change_failure_rate_pct; reliability_pct; created_at; updated_at; created_by; updated_by; deleted_at</x:v>
       </x:c>
-      <x:c r="W102" s="5" t="str">
+      <x:c r="X102" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X102" s="5" t="str">
+      <x:c r="Y102" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -7745,30 +8052,33 @@
       </x:c>
       <x:c r="O103" s="5" t="str"/>
       <x:c r="P103" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q103" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R103" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R103" s="5" t="str">
+      <x:c r="S103" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S103" s="5" t="str">
+      <x:c r="T103" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T103" s="5" t="str">
+      <x:c r="U103" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U103" s="5" t="str">
+      <x:c r="V103" s="5" t="str">
         <x:v>supabase/migrations/002_engagement_engine.sql; supabase/migrations/013_engagement_state.sql</x:v>
       </x:c>
-      <x:c r="V103" s="5" t="str">
+      <x:c r="W103" s="5" t="str">
         <x:v>id; client_id; solution; status; current_phase; maestro_id; started_at; created_by; metadata; graph_node_id; name; industry_code; function_code; objective_code; topic_code; sponsor_person_id; co_sponsor_person_id; maestro_person_id; charter; gates_passed; decisions; deliverables; sponsor_approvals; baseline_metrics</x:v>
       </x:c>
-      <x:c r="W103" s="5" t="str">
+      <x:c r="X103" s="5" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="X103" s="5" t="str">
+      <x:c r="Y103" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -7817,30 +8127,33 @@
       </x:c>
       <x:c r="O104" s="5" t="str"/>
       <x:c r="P104" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q104" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R104" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R104" s="5" t="str">
+      <x:c r="S104" s="5" t="str">
         <x:v>Contains enterprise-meaningful accepted, factual, commercial, metric, risk, or control data that should link through canonical IDs after review.</x:v>
       </x:c>
-      <x:c r="S104" s="5" t="str">
+      <x:c r="T104" s="5" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="T104" s="5" t="str">
+      <x:c r="U104" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U104" s="5" t="str">
+      <x:c r="V104" s="5" t="str">
         <x:v>supabase/migrations/20260514100000_enterprise_context_layer.sql</x:v>
       </x:c>
-      <x:c r="V104" s="5" t="str">
+      <x:c r="W104" s="5" t="str">
         <x:v>id; client_id; tenant_key; canonical_record_id; record_type; record_subtype; title; source_id; source_file_id; source_system; source_record_id; source_file; source_sheet; source_row_number; owner; steward_owner; last_synced_at; last_validated_at; confidence; freshness_status; evidence_pointer; lifecycle_state; superseded_by_record_id; payload_hash</x:v>
       </x:c>
-      <x:c r="W104" s="5" t="str">
+      <x:c r="X104" s="5" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="X104" s="5" t="str">
+      <x:c r="Y104" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -7889,30 +8202,33 @@
       </x:c>
       <x:c r="O105" s="5" t="str"/>
       <x:c r="P105" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q105" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R105" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R105" s="5" t="str">
+      <x:c r="S105" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S105" s="5" t="str">
+      <x:c r="T105" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T105" s="5" t="str">
+      <x:c r="U105" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U105" s="5" t="str">
+      <x:c r="V105" s="5" t="str">
         <x:v>supabase/migrations/20260523090000_client_extension_it_productivity.sql</x:v>
       </x:c>
-      <x:c r="V105" s="5" t="str">
+      <x:c r="W105" s="5" t="str">
         <x:v>id; client_id; move_id; gate_id; criterion_name; threshold_numeric; current_value; status; evaluated_at; created_at; updated_at; created_by; updated_by; deleted_at</x:v>
       </x:c>
-      <x:c r="W105" s="5" t="str">
+      <x:c r="X105" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X105" s="5" t="str">
+      <x:c r="Y105" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -7961,30 +8277,33 @@
       </x:c>
       <x:c r="O106" s="5" t="str"/>
       <x:c r="P106" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q106" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R106" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R106" s="5" t="str">
+      <x:c r="S106" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S106" s="5" t="str">
+      <x:c r="T106" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T106" s="5" t="str">
+      <x:c r="U106" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U106" s="5" t="str">
+      <x:c r="V106" s="5" t="str">
         <x:v>supabase/migrations/20260723233000_pricing_reference_schema_v1.sql</x:v>
       </x:c>
-      <x:c r="V106" s="5" t="str">
+      <x:c r="W106" s="5" t="str">
         <x:v>id; taxonomy_version; tower_code; tower_name; scope; source_artifact; source_row; source_label; status; tenant_key; content_hash; created_at</x:v>
       </x:c>
-      <x:c r="W106" s="5" t="str">
+      <x:c r="X106" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X106" s="5" t="str">
+      <x:c r="Y106" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -8036,27 +8355,30 @@
         <x:v>knowledge.program</x:v>
       </x:c>
       <x:c r="Q107" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R107" s="5" t="str">
         <x:v>archive</x:v>
       </x:c>
-      <x:c r="R107" s="5" t="str">
+      <x:c r="S107" s="5" t="str">
         <x:v>Audit/history object should be retained but not promoted as enterprise truth.</x:v>
       </x:c>
-      <x:c r="S107" s="5" t="str">
+      <x:c r="T107" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T107" s="5" t="str">
+      <x:c r="U107" s="5" t="str">
         <x:v>Archive-only; no runtime cutover.</x:v>
       </x:c>
-      <x:c r="U107" s="5" t="str">
+      <x:c r="V107" s="5" t="str">
         <x:v>supabase/migrations/20260430140000_program_audit_log.sql</x:v>
       </x:c>
-      <x:c r="V107" s="5" t="str">
+      <x:c r="W107" s="5" t="str">
         <x:v>id; tenant_key; program_id; engagement_id; actor_id; actor_role; action; from_state; to_state; rationale; evidence_refs; created_at</x:v>
       </x:c>
-      <x:c r="W107" s="5" t="str">
+      <x:c r="X107" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X107" s="5" t="str">
+      <x:c r="Y107" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -8105,30 +8427,33 @@
       </x:c>
       <x:c r="O108" s="5" t="str"/>
       <x:c r="P108" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q108" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R108" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R108" s="5" t="str">
+      <x:c r="S108" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S108" s="5" t="str">
+      <x:c r="T108" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T108" s="5" t="str">
+      <x:c r="U108" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U108" s="5" t="str">
+      <x:c r="V108" s="5" t="str">
         <x:v>supabase/migrations/20260523090000_client_extension_it_productivity.sql</x:v>
       </x:c>
-      <x:c r="V108" s="5" t="str">
+      <x:c r="W108" s="5" t="str">
         <x:v>id; client_id; role_id; title; fte_count; source; geo; ladder_level; function_area; created_at; updated_at; created_by; updated_by; deleted_at</x:v>
       </x:c>
-      <x:c r="W108" s="5" t="str">
+      <x:c r="X108" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X108" s="5" t="str">
+      <x:c r="Y108" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -8177,30 +8502,33 @@
       </x:c>
       <x:c r="O109" s="5" t="str"/>
       <x:c r="P109" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q109" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R109" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R109" s="5" t="str">
+      <x:c r="S109" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S109" s="5" t="str">
+      <x:c r="T109" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T109" s="5" t="str">
+      <x:c r="U109" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U109" s="5" t="str">
+      <x:c r="V109" s="5" t="str">
         <x:v>supabase/migrations/018_teams_and_memberships.sql</x:v>
       </x:c>
-      <x:c r="V109" s="5" t="str">
+      <x:c r="W109" s="5" t="str">
         <x:v>id; name; slug; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W109" s="5" t="str">
+      <x:c r="X109" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X109" s="5" t="str">
+      <x:c r="Y109" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -8249,30 +8577,33 @@
       </x:c>
       <x:c r="O110" s="5" t="str"/>
       <x:c r="P110" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q110" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R110" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R110" s="5" t="str">
+      <x:c r="S110" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S110" s="5" t="str">
+      <x:c r="T110" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T110" s="5" t="str">
+      <x:c r="U110" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U110" s="5" t="str">
+      <x:c r="V110" s="5" t="str">
         <x:v>supabase/migrations/20260525060000_tower_ai_tool_usage.sql; supabase/migrations/20260530120000_tower_ai_tool_usage.sql</x:v>
       </x:c>
-      <x:c r="V110" s="5" t="str">
+      <x:c r="W110" s="5" t="str">
         <x:v>id; client_id; tool; team; period_start; period_end; active_users; total_suggestions; accepted_suggestions; acceptance_rate_pct; monthly_cost_usd; seats_assigned; seats_used; source_file_id; ingest_run_id; raw_jsonb; created_at; updated_at; completions_shown; completions_accepted; ingested_at</x:v>
       </x:c>
-      <x:c r="W110" s="5" t="str">
+      <x:c r="X110" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X110" s="5" t="str">
+      <x:c r="Y110" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -8321,30 +8652,33 @@
       </x:c>
       <x:c r="O111" s="5" t="str"/>
       <x:c r="P111" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q111" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R111" s="5" t="str">
         <x:v>archive</x:v>
       </x:c>
-      <x:c r="R111" s="5" t="str">
+      <x:c r="S111" s="5" t="str">
         <x:v>Audit/history object should be retained but not promoted as enterprise truth.</x:v>
       </x:c>
-      <x:c r="S111" s="5" t="str">
+      <x:c r="T111" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T111" s="5" t="str">
+      <x:c r="U111" s="5" t="str">
         <x:v>Archive-only; no runtime cutover.</x:v>
       </x:c>
-      <x:c r="U111" s="5" t="str">
+      <x:c r="V111" s="5" t="str">
         <x:v>supabase/migrations/20260626130000_tower_demo_readiness_materialized_plane.sql</x:v>
       </x:c>
-      <x:c r="V111" s="5" t="str">
+      <x:c r="W111" s="5" t="str">
         <x:v>id; client_id; tenant_key; surface; question; generated_system_prompt; generated_user_prompt; claude_raw_response; parser_result; final_answer; rendered_artifacts; validation_result; translation_warnings; model; fallback_used; fallback_reason; latency_ms; created_at</x:v>
       </x:c>
-      <x:c r="W111" s="5" t="str">
+      <x:c r="X111" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X111" s="5" t="str">
+      <x:c r="Y111" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -8395,30 +8729,33 @@
         <x:v>Metric/value/cost family candidate</x:v>
       </x:c>
       <x:c r="P112" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q112" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R112" s="5" t="str">
         <x:v>project_shared_consumption</x:v>
       </x:c>
-      <x:c r="R112" s="5" t="str">
+      <x:c r="S112" s="5" t="str">
         <x:v>Derived object shaped for reuse by screens, reports, exports, or aVa.</x:v>
       </x:c>
-      <x:c r="S112" s="5" t="str">
+      <x:c r="T112" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="T112" s="5" t="str">
+      <x:c r="U112" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="U112" s="5" t="str">
+      <x:c r="V112" s="5" t="str">
         <x:v>supabase/migrations/20260626203000_tower_budget_rollups.sql</x:v>
       </x:c>
-      <x:c r="V112" s="5" t="str">
+      <x:c r="W112" s="5" t="str">
         <x:v>id; client_id; tenant_key; period_label; fiscal_year; portfolio_company; total_it_budget_usd; actual_spend_ytd_usd; forecast_spend_usd; opex_amount_usd; capex_amount_usd; run_amount_usd; change_amount_usd; vendor_amount_usd; labor_amount_usd; revenue_usd; employees; it_spend_as_pct_revenue; source_file; lineage; created_at; updated_at; AND</x:v>
       </x:c>
-      <x:c r="W112" s="5" t="str">
+      <x:c r="X112" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X112" s="5" t="str">
+      <x:c r="Y112" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -8467,30 +8804,33 @@
       </x:c>
       <x:c r="O113" s="5" t="str"/>
       <x:c r="P113" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q113" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R113" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R113" s="5" t="str">
+      <x:c r="S113" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S113" s="5" t="str">
+      <x:c r="T113" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T113" s="5" t="str">
+      <x:c r="U113" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U113" s="5" t="str">
+      <x:c r="V113" s="5" t="str">
         <x:v>supabase/migrations/20260530220000_tower_claude_code_usage.sql</x:v>
       </x:c>
-      <x:c r="V113" s="5" t="str">
+      <x:c r="W113" s="5" t="str">
         <x:v>id; tenant_client_key; team; developer_id; period_start; period_end; sessions; prompt_tokens; output_tokens; monthly_cost_usd; primary_use_case; source_file; ingested_at</x:v>
       </x:c>
-      <x:c r="W113" s="5" t="str">
+      <x:c r="X113" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X113" s="5" t="str">
+      <x:c r="Y113" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -8541,30 +8881,33 @@
         <x:v>Metric/value/cost family candidate</x:v>
       </x:c>
       <x:c r="P114" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q114" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R114" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R114" s="5" t="str">
+      <x:c r="S114" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S114" s="5" t="str">
+      <x:c r="T114" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T114" s="5" t="str">
+      <x:c r="U114" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U114" s="5" t="str">
+      <x:c r="V114" s="5" t="str">
         <x:v>supabase/migrations/20260530140000_tower_cloud_cost.sql</x:v>
       </x:c>
-      <x:c r="V114" s="5" t="str">
+      <x:c r="W114" s="5" t="str">
         <x:v>id; client_id; subscription_id; resource_group; resource_name; service; meter_category; location; tag_program; tag_environment; period_start; period_end; monthly_cost_usd; currency; source; source_file_id; ingested_at</x:v>
       </x:c>
-      <x:c r="W114" s="5" t="str">
+      <x:c r="X114" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X114" s="5" t="str">
+      <x:c r="Y114" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -8616,27 +8959,30 @@
         <x:v>knowledge.application</x:v>
       </x:c>
       <x:c r="Q115" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R115" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R115" s="5" t="str">
+      <x:c r="S115" s="5" t="str">
         <x:v>CMDB configuration items can link to canonical application/system/service identity after quality review.</x:v>
       </x:c>
-      <x:c r="S115" s="5" t="str">
+      <x:c r="T115" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="T115" s="5" t="str">
+      <x:c r="U115" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U115" s="5" t="str">
+      <x:c r="V115" s="5" t="str">
         <x:v>supabase/migrations/20260530120000_tower_cmdb.sql; supabase/migrations/20260717063000_tower_foundation_tables_ledger_repair.sql</x:v>
       </x:c>
-      <x:c r="V115" s="5" t="str">
+      <x:c r="W115" s="5" t="str">
         <x:v>id; client_id; ci_sys_id; ci_name; ci_type; ci_class; lifecycle_state; owner_team; business_service; criticality; environment; source_system; ingest_run_id; ingested_at; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W115" s="5" t="str">
+      <x:c r="X115" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X115" s="5" t="str">
+      <x:c r="Y115" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -8688,27 +9034,30 @@
         <x:v>knowledge.relationship_projection</x:v>
       </x:c>
       <x:c r="Q116" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R116" s="5" t="str">
         <x:v>project_shared_consumption</x:v>
       </x:c>
-      <x:c r="R116" s="5" t="str">
+      <x:c r="S116" s="5" t="str">
         <x:v>CMDB dependencies should publish as governed relationship/graph projections after endpoint validation.</x:v>
       </x:c>
-      <x:c r="S116" s="5" t="str">
+      <x:c r="T116" s="5" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="T116" s="5" t="str">
+      <x:c r="U116" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="U116" s="5" t="str">
+      <x:c r="V116" s="5" t="str">
         <x:v>supabase/migrations/20260530120000_tower_cmdb.sql; supabase/migrations/20260717063000_tower_foundation_tables_ledger_repair.sql</x:v>
       </x:c>
-      <x:c r="V116" s="5" t="str">
+      <x:c r="W116" s="5" t="str">
         <x:v>id; client_id; source_ci_sys_id; target_ci_sys_id; dependency_type; source_system; ingest_run_id; ingested_at; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W116" s="5" t="str">
+      <x:c r="X116" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X116" s="5" t="str">
+      <x:c r="Y116" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -8762,27 +9111,30 @@
         <x:v>knowledge.metric_observation</x:v>
       </x:c>
       <x:c r="Q117" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R117" s="5" t="str">
         <x:v>project_shared_consumption</x:v>
       </x:c>
-      <x:c r="R117" s="5" t="str">
+      <x:c r="S117" s="5" t="str">
         <x:v>DORA values are metric observations and should consume governed metric definitions.</x:v>
       </x:c>
-      <x:c r="S117" s="5" t="str">
+      <x:c r="T117" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="T117" s="5" t="str">
+      <x:c r="U117" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="U117" s="5" t="str">
+      <x:c r="V117" s="5" t="str">
         <x:v>supabase/migrations/20260530133918_tower_dora_metrics.sql</x:v>
       </x:c>
-      <x:c r="V117" s="5" t="str">
+      <x:c r="W117" s="5" t="str">
         <x:v>id; client_id; repo; team; period_start; period_end; deployment_frequency_per_day; lead_time_for_changes_hours; change_failure_rate_pct; mttr_hours; sample_size_deploys; source; source_file_id; created_at; updated_at; created_by; updated_by; deleted_at</x:v>
       </x:c>
-      <x:c r="W117" s="5" t="str">
+      <x:c r="X117" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X117" s="5" t="str">
+      <x:c r="Y117" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -8831,30 +9183,33 @@
       </x:c>
       <x:c r="O118" s="5" t="str"/>
       <x:c r="P118" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q118" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R118" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R118" s="5" t="str">
+      <x:c r="S118" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S118" s="5" t="str">
+      <x:c r="T118" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T118" s="5" t="str">
+      <x:c r="U118" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U118" s="5" t="str">
+      <x:c r="V118" s="5" t="str">
         <x:v>supabase/migrations/20260626130000_tower_demo_readiness_materialized_plane.sql</x:v>
       </x:c>
-      <x:c r="V118" s="5" t="str">
+      <x:c r="W118" s="5" t="str">
         <x:v>id; tenant_key; identifier; identifier_type; severity; active; reason; created_at</x:v>
       </x:c>
-      <x:c r="W118" s="5" t="str">
+      <x:c r="X118" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X118" s="5" t="str">
+      <x:c r="Y118" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -8903,30 +9258,33 @@
       </x:c>
       <x:c r="O119" s="5" t="str"/>
       <x:c r="P119" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q119" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R119" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R119" s="5" t="str">
+      <x:c r="S119" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S119" s="5" t="str">
+      <x:c r="T119" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T119" s="5" t="str">
+      <x:c r="U119" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U119" s="5" t="str">
+      <x:c r="V119" s="5" t="str">
         <x:v>supabase/migrations/20260626130000_tower_demo_readiness_materialized_plane.sql</x:v>
       </x:c>
-      <x:c r="V119" s="5" t="str">
+      <x:c r="W119" s="5" t="str">
         <x:v>id; client_id; tenant_key; gap_key; gap_type; label; impact; required_source; severity; surface; status; lineage; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W119" s="5" t="str">
+      <x:c r="X119" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X119" s="5" t="str">
+      <x:c r="Y119" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -8975,30 +9333,33 @@
       </x:c>
       <x:c r="O120" s="5" t="str"/>
       <x:c r="P120" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q120" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R120" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R120" s="5" t="str">
+      <x:c r="S120" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S120" s="5" t="str">
+      <x:c r="T120" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T120" s="5" t="str">
+      <x:c r="U120" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U120" s="5" t="str">
+      <x:c r="V120" s="5" t="str">
         <x:v>supabase/migrations/20260530120000_tower_itsm_records.sql</x:v>
       </x:c>
-      <x:c r="V120" s="5" t="str">
+      <x:c r="W120" s="5" t="str">
         <x:v>id; tenant_key; record_number; record_type; priority; service; assignment_group; opened_at; closed_at; mttr_minutes; change_success; source; source_file_id; ingested_at</x:v>
       </x:c>
-      <x:c r="W120" s="5" t="str">
+      <x:c r="X120" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X120" s="5" t="str">
+      <x:c r="Y120" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -9047,30 +9408,33 @@
       </x:c>
       <x:c r="O121" s="5" t="str"/>
       <x:c r="P121" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q121" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R121" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R121" s="5" t="str">
+      <x:c r="S121" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S121" s="5" t="str">
+      <x:c r="T121" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T121" s="5" t="str">
+      <x:c r="U121" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U121" s="5" t="str">
+      <x:c r="V121" s="5" t="str">
         <x:v>supabase/migrations/20260530120000_tower_jira_issues.sql</x:v>
       </x:c>
-      <x:c r="V121" s="5" t="str">
+      <x:c r="W121" s="5" t="str">
         <x:v>id; client_id; issue_key; issue_type; epic_key; team; status; story_points; created_at; started_at; completed_at; cycle_time_hours; source_file; ingested_at</x:v>
       </x:c>
-      <x:c r="W121" s="5" t="str">
+      <x:c r="X121" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X121" s="5" t="str">
+      <x:c r="Y121" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -9119,30 +9483,33 @@
       </x:c>
       <x:c r="O122" s="5" t="str"/>
       <x:c r="P122" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q122" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R122" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R122" s="5" t="str">
+      <x:c r="S122" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S122" s="5" t="str">
+      <x:c r="T122" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T122" s="5" t="str">
+      <x:c r="U122" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U122" s="5" t="str">
+      <x:c r="V122" s="5" t="str">
         <x:v>supabase/migrations/20260626130000_tower_demo_readiness_materialized_plane.sql</x:v>
       </x:c>
-      <x:c r="V122" s="5" t="str">
+      <x:c r="W122" s="5" t="str">
         <x:v>id; client_id; tenant_key; scope_key; scope_type; scope_label; view_key; prompt_version; dossier_version; stage1_status; stage2_status; coverage_score; verdict; dossier; validation_result; lineage; created_at</x:v>
       </x:c>
-      <x:c r="W122" s="5" t="str">
+      <x:c r="X122" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X122" s="5" t="str">
+      <x:c r="Y122" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -9191,30 +9558,33 @@
       </x:c>
       <x:c r="O123" s="5" t="str"/>
       <x:c r="P123" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q123" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R123" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R123" s="5" t="str">
+      <x:c r="S123" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S123" s="5" t="str">
+      <x:c r="T123" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T123" s="5" t="str">
+      <x:c r="U123" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U123" s="5" t="str">
+      <x:c r="V123" s="5" t="str">
         <x:v>supabase/migrations/20260626130000_tower_demo_readiness_materialized_plane.sql</x:v>
       </x:c>
-      <x:c r="V123" s="5" t="str">
+      <x:c r="W123" s="5" t="str">
         <x:v>id; client_id; tenant_key; source_set; status; started_at; completed_at; notes; created_at</x:v>
       </x:c>
-      <x:c r="W123" s="5" t="str">
+      <x:c r="X123" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X123" s="5" t="str">
+      <x:c r="Y123" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -9268,27 +9638,30 @@
         <x:v>knowledge.metric_observation</x:v>
       </x:c>
       <x:c r="Q124" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R124" s="5" t="str">
         <x:v>project_shared_consumption</x:v>
       </x:c>
-      <x:c r="R124" s="5" t="str">
+      <x:c r="S124" s="5" t="str">
         <x:v>Program financial observations should publish through metric/value projections, not become a second financial truth.</x:v>
       </x:c>
-      <x:c r="S124" s="5" t="str">
+      <x:c r="T124" s="5" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="T124" s="5" t="str">
+      <x:c r="U124" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="U124" s="5" t="str">
+      <x:c r="V124" s="5" t="str">
         <x:v>supabase/migrations/20260530134228_tower_program_financials.sql</x:v>
       </x:c>
-      <x:c r="V124" s="5" t="str">
+      <x:c r="W124" s="5" t="str">
         <x:v>id; client_id; program_id; period_start; period_end; budget_usd; actual_usd; capex_usd; opex_usd; vendor_id; cost_center; gl_account; source; source_file_id; source_system; created_at; updated_at; OR</x:v>
       </x:c>
-      <x:c r="W124" s="5" t="str">
+      <x:c r="X124" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X124" s="5" t="str">
+      <x:c r="Y124" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -9340,27 +9713,30 @@
         <x:v>knowledge.program</x:v>
       </x:c>
       <x:c r="Q125" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R125" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R125" s="5" t="str">
+      <x:c r="S125" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S125" s="5" t="str">
+      <x:c r="T125" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T125" s="5" t="str">
+      <x:c r="U125" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U125" s="5" t="str">
+      <x:c r="V125" s="5" t="str">
         <x:v>supabase/migrations/20260626130000_tower_demo_readiness_materialized_plane.sql</x:v>
       </x:c>
-      <x:c r="V125" s="5" t="str">
+      <x:c r="W125" s="5" t="str">
         <x:v>id; materialization_run_id; client_id; tenant_key; period_label; initiative_id; display_id; name; description; category_id; category_name; goal_id; goal_name; stage; stage_detail; owner_name; owner_title; owner_function; committed_annual_usd; committed_total_usd; measured_value_usd; status_flag; status_summary; confidence_level</x:v>
       </x:c>
-      <x:c r="W125" s="5" t="str">
+      <x:c r="X125" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X125" s="5" t="str">
+      <x:c r="Y125" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -9412,27 +9788,30 @@
         <x:v>knowledge.vendor</x:v>
       </x:c>
       <x:c r="Q126" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R126" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R126" s="5" t="str">
+      <x:c r="S126" s="5" t="str">
         <x:v>Contains enterprise-meaningful accepted, factual, commercial, metric, risk, or control data that should link through canonical IDs after review.</x:v>
       </x:c>
-      <x:c r="S126" s="5" t="str">
+      <x:c r="T126" s="5" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="T126" s="5" t="str">
+      <x:c r="U126" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U126" s="5" t="str">
+      <x:c r="V126" s="5" t="str">
         <x:v>supabase/migrations/20260626130000_tower_demo_readiness_materialized_plane.sql</x:v>
       </x:c>
-      <x:c r="V126" s="5" t="str">
+      <x:c r="W126" s="5" t="str">
         <x:v>id; materialization_run_id; client_id; tenant_key; period_label; vendor_id; vendor_name; logical_vendor_key; initiative_id; initiative_display_id; initiative_name; contract_value_usd; renewal_date; financial_health; amount_type; accounting_treatment; spend_posture; scope_type; allocation_method; is_duplicate_rollup; duplicate_group_key; duplicate_raw_row_count; is_synthetic; is_outlier</x:v>
       </x:c>
-      <x:c r="W126" s="5" t="str">
+      <x:c r="X126" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X126" s="5" t="str">
+      <x:c r="Y126" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -9483,30 +9862,33 @@
         <x:v>Metric/value/cost family candidate</x:v>
       </x:c>
       <x:c r="P127" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q127" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R127" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R127" s="5" t="str">
+      <x:c r="S127" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S127" s="5" t="str">
+      <x:c r="T127" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T127" s="5" t="str">
+      <x:c r="U127" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U127" s="5" t="str">
+      <x:c r="V127" s="5" t="str">
         <x:v>supabase/migrations/20260626130000_tower_demo_readiness_materialized_plane.sql</x:v>
       </x:c>
-      <x:c r="V127" s="5" t="str">
+      <x:c r="W127" s="5" t="str">
         <x:v>id; client_id; tenant_key; object_type; object_key; source_value_usd; recomputed_value_usd; benchmark_unit_price_usd; seat_count; amount_type; verdict; rule_key; notes; lineage; created_at</x:v>
       </x:c>
-      <x:c r="W127" s="5" t="str">
+      <x:c r="X127" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X127" s="5" t="str">
+      <x:c r="Y127" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -9555,30 +9937,33 @@
       </x:c>
       <x:c r="O128" s="5" t="str"/>
       <x:c r="P128" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q128" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R128" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R128" s="5" t="str">
+      <x:c r="S128" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S128" s="5" t="str">
+      <x:c r="T128" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T128" s="5" t="str">
+      <x:c r="U128" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U128" s="5" t="str">
+      <x:c r="V128" s="5" t="str">
         <x:v>supabase/migrations/20260421151300_tower_user_preferences.sql</x:v>
       </x:c>
-      <x:c r="V128" s="5" t="str">
+      <x:c r="W128" s="5" t="str">
         <x:v>id; person_id; client_id; dashboard_variant; default_surface; default_filters; atlas_panel_state; mobile_summary_enabled; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W128" s="5" t="str">
+      <x:c r="X128" s="5" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="X128" s="5" t="str">
+      <x:c r="Y128" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -9632,27 +10017,30 @@
         <x:v>knowledge.metric_observation</x:v>
       </x:c>
       <x:c r="Q129" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R129" s="5" t="str">
         <x:v>project_shared_consumption</x:v>
       </x:c>
-      <x:c r="R129" s="5" t="str">
+      <x:c r="S129" s="5" t="str">
         <x:v>Vendor-spend observations should publish through shared spend/value projections with canonical vendor links.</x:v>
       </x:c>
-      <x:c r="S129" s="5" t="str">
+      <x:c r="T129" s="5" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="T129" s="5" t="str">
+      <x:c r="U129" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="U129" s="5" t="str">
+      <x:c r="V129" s="5" t="str">
         <x:v>supabase/migrations/20260530134228_tower_program_financials.sql</x:v>
       </x:c>
-      <x:c r="V129" s="5" t="str">
+      <x:c r="W129" s="5" t="str">
         <x:v>id; client_id; vendor_id; vendor_name; cost_center; gl_account; ttm_spend_usd; source; source_file_id; source_system; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W129" s="5" t="str">
+      <x:c r="X129" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X129" s="5" t="str">
+      <x:c r="Y129" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -9701,30 +10089,33 @@
       </x:c>
       <x:c r="O130" s="5" t="str"/>
       <x:c r="P130" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q130" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R130" s="5" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R130" s="5" t="str">
+      <x:c r="S130" s="5" t="str">
         <x:v>Needed for domain workflow unless a later live data review proves it obsolete.</x:v>
       </x:c>
-      <x:c r="S130" s="5" t="str">
+      <x:c r="T130" s="5" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T130" s="5" t="str">
+      <x:c r="U130" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U130" s="5" t="str">
+      <x:c r="V130" s="5" t="str">
         <x:v>supabase/migrations/20260530134151_tower_workforce.sql; supabase/migrations/20260717063000_tower_foundation_tables_ledger_repair.sql</x:v>
       </x:c>
-      <x:c r="V130" s="5" t="str">
+      <x:c r="W130" s="5" t="str">
         <x:v>id; client_id; employee_id; function; sub_function; location; level; contractor_flag; start_date; attrition_date; attrition_reason; source_file_id; ingested_at; as_of_date; data_class</x:v>
       </x:c>
-      <x:c r="W130" s="5" t="str">
+      <x:c r="X130" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X130" s="5" t="str">
+      <x:c r="Y130" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -9776,27 +10167,30 @@
         <x:v>knowledge.program</x:v>
       </x:c>
       <x:c r="Q131" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="R131" s="5" t="str">
         <x:v>promote_link_canonical_knowledge</x:v>
       </x:c>
-      <x:c r="R131" s="5" t="str">
+      <x:c r="S131" s="5" t="str">
         <x:v>Use cases and initiatives are enterprise program/opportunity objects once reviewed.</x:v>
       </x:c>
-      <x:c r="S131" s="5" t="str">
+      <x:c r="T131" s="5" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="T131" s="5" t="str">
+      <x:c r="U131" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="U131" s="5" t="str">
+      <x:c r="V131" s="5" t="str">
         <x:v>supabase/migrations/022_tower_data_model.sql</x:v>
       </x:c>
-      <x:c r="V131" s="5" t="str">
+      <x:c r="W131" s="5" t="str">
         <x:v>id; client_id; name; description; business_unit; domain; sponsor_person_id; owner_person_id; stage; systems; ai_type; scope; vendor; source; source_engagement_id; source_file_id; external_id; metadata; created_at; updated_at</x:v>
       </x:c>
-      <x:c r="W131" s="5" t="str">
+      <x:c r="X131" s="5" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X131" s="5" t="str">
+      <x:c r="Y131" s="5" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
@@ -9847,30 +10241,33 @@
         <x:v>Metric/value/cost family candidate</x:v>
       </x:c>
       <x:c r="P132" s="6" t="str">
-        <x:v>knowledge.metric</x:v>
+        <x:v>to_be_mapped_after_live_profile</x:v>
       </x:c>
       <x:c r="Q132" s="6" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="R132" s="6" t="str">
         <x:v>retain_operational</x:v>
       </x:c>
-      <x:c r="R132" s="6" t="str">
+      <x:c r="S132" s="6" t="str">
         <x:v>Workflow, review, template, or draft state remains domain-owned unless it emits accepted/published facts.</x:v>
       </x:c>
-      <x:c r="S132" s="6" t="str">
+      <x:c r="T132" s="6" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="T132" s="6" t="str">
+      <x:c r="U132" s="6" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="U132" s="6" t="str">
+      <x:c r="V132" s="6" t="str">
         <x:v>supabase/migrations/20260523090000_client_extension_it_productivity.sql</x:v>
       </x:c>
-      <x:c r="V132" s="6" t="str">
+      <x:c r="W132" s="6" t="str">
         <x:v>id; client_id; move_id; layer_type; projected_jsonb; tracked_jsonb; verified_jsonb; attested_by; attested_at; created_at; updated_at; created_by; updated_by; deleted_at</x:v>
       </x:c>
-      <x:c r="W132" s="6" t="str">
+      <x:c r="X132" s="6" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="X132" s="6" t="str">
+      <x:c r="Y132" s="6" t="str">
         <x:v>high: migration DDL parsed</x:v>
       </x:c>
     </x:row>
